--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -1,77 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605867A4-3220-41E4-82F8-5977B943EEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="2016" yWindow="756" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eGnJ0erqkwmpLAbSFXzXqD33NZjjF+BEV5V8qOaTQi0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>초기 생성될 수치</t>
+  </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>초기 생성될 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>InitSize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Pool_Jewel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Pool_Tool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InteractableContainer_Prefab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -80,55 +64,50 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="5B9BD5"/>
@@ -152,79 +131,19 @@
         <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -365,63 +284,1063 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.71"/>
+    <col customWidth="1" min="2" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B1" t="s">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" ht="17.25" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>10</v>
+      <c r="B4" s="1">
+        <v>10.0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>5</v>
+      <c r="B5" s="1">
+        <v>5.0</v>
       </c>
     </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1"/>
+    <row r="8" ht="17.25" customHeight="1"/>
+    <row r="9" ht="17.25" customHeight="1"/>
+    <row r="10" ht="17.25" customHeight="1"/>
+    <row r="11" ht="17.25" customHeight="1"/>
+    <row r="12" ht="17.25" customHeight="1"/>
+    <row r="13" ht="17.25" customHeight="1"/>
+    <row r="14" ht="17.25" customHeight="1"/>
+    <row r="15" ht="17.25" customHeight="1"/>
+    <row r="16" ht="17.25" customHeight="1"/>
+    <row r="17" ht="17.25" customHeight="1"/>
+    <row r="18" ht="17.25" customHeight="1"/>
+    <row r="19" ht="17.25" customHeight="1"/>
+    <row r="20" ht="17.25" customHeight="1"/>
+    <row r="21" ht="17.25" customHeight="1"/>
+    <row r="22" ht="17.25" customHeight="1"/>
+    <row r="23" ht="17.25" customHeight="1"/>
+    <row r="24" ht="17.25" customHeight="1"/>
+    <row r="25" ht="17.25" customHeight="1"/>
+    <row r="26" ht="17.25" customHeight="1"/>
+    <row r="27" ht="17.25" customHeight="1"/>
+    <row r="28" ht="17.25" customHeight="1"/>
+    <row r="29" ht="17.25" customHeight="1"/>
+    <row r="30" ht="17.25" customHeight="1"/>
+    <row r="31" ht="17.25" customHeight="1"/>
+    <row r="32" ht="17.25" customHeight="1"/>
+    <row r="33" ht="17.25" customHeight="1"/>
+    <row r="34" ht="17.25" customHeight="1"/>
+    <row r="35" ht="17.25" customHeight="1"/>
+    <row r="36" ht="17.25" customHeight="1"/>
+    <row r="37" ht="17.25" customHeight="1"/>
+    <row r="38" ht="17.25" customHeight="1"/>
+    <row r="39" ht="17.25" customHeight="1"/>
+    <row r="40" ht="17.25" customHeight="1"/>
+    <row r="41" ht="17.25" customHeight="1"/>
+    <row r="42" ht="17.25" customHeight="1"/>
+    <row r="43" ht="17.25" customHeight="1"/>
+    <row r="44" ht="17.25" customHeight="1"/>
+    <row r="45" ht="17.25" customHeight="1"/>
+    <row r="46" ht="17.25" customHeight="1"/>
+    <row r="47" ht="17.25" customHeight="1"/>
+    <row r="48" ht="17.25" customHeight="1"/>
+    <row r="49" ht="17.25" customHeight="1"/>
+    <row r="50" ht="17.25" customHeight="1"/>
+    <row r="51" ht="17.25" customHeight="1"/>
+    <row r="52" ht="17.25" customHeight="1"/>
+    <row r="53" ht="17.25" customHeight="1"/>
+    <row r="54" ht="17.25" customHeight="1"/>
+    <row r="55" ht="17.25" customHeight="1"/>
+    <row r="56" ht="17.25" customHeight="1"/>
+    <row r="57" ht="17.25" customHeight="1"/>
+    <row r="58" ht="17.25" customHeight="1"/>
+    <row r="59" ht="17.25" customHeight="1"/>
+    <row r="60" ht="17.25" customHeight="1"/>
+    <row r="61" ht="17.25" customHeight="1"/>
+    <row r="62" ht="17.25" customHeight="1"/>
+    <row r="63" ht="17.25" customHeight="1"/>
+    <row r="64" ht="17.25" customHeight="1"/>
+    <row r="65" ht="17.25" customHeight="1"/>
+    <row r="66" ht="17.25" customHeight="1"/>
+    <row r="67" ht="17.25" customHeight="1"/>
+    <row r="68" ht="17.25" customHeight="1"/>
+    <row r="69" ht="17.25" customHeight="1"/>
+    <row r="70" ht="17.25" customHeight="1"/>
+    <row r="71" ht="17.25" customHeight="1"/>
+    <row r="72" ht="17.25" customHeight="1"/>
+    <row r="73" ht="17.25" customHeight="1"/>
+    <row r="74" ht="17.25" customHeight="1"/>
+    <row r="75" ht="17.25" customHeight="1"/>
+    <row r="76" ht="17.25" customHeight="1"/>
+    <row r="77" ht="17.25" customHeight="1"/>
+    <row r="78" ht="17.25" customHeight="1"/>
+    <row r="79" ht="17.25" customHeight="1"/>
+    <row r="80" ht="17.25" customHeight="1"/>
+    <row r="81" ht="17.25" customHeight="1"/>
+    <row r="82" ht="17.25" customHeight="1"/>
+    <row r="83" ht="17.25" customHeight="1"/>
+    <row r="84" ht="17.25" customHeight="1"/>
+    <row r="85" ht="17.25" customHeight="1"/>
+    <row r="86" ht="17.25" customHeight="1"/>
+    <row r="87" ht="17.25" customHeight="1"/>
+    <row r="88" ht="17.25" customHeight="1"/>
+    <row r="89" ht="17.25" customHeight="1"/>
+    <row r="90" ht="17.25" customHeight="1"/>
+    <row r="91" ht="17.25" customHeight="1"/>
+    <row r="92" ht="17.25" customHeight="1"/>
+    <row r="93" ht="17.25" customHeight="1"/>
+    <row r="94" ht="17.25" customHeight="1"/>
+    <row r="95" ht="17.25" customHeight="1"/>
+    <row r="96" ht="17.25" customHeight="1"/>
+    <row r="97" ht="17.25" customHeight="1"/>
+    <row r="98" ht="17.25" customHeight="1"/>
+    <row r="99" ht="17.25" customHeight="1"/>
+    <row r="100" ht="17.25" customHeight="1"/>
+    <row r="101" ht="17.25" customHeight="1"/>
+    <row r="102" ht="17.25" customHeight="1"/>
+    <row r="103" ht="17.25" customHeight="1"/>
+    <row r="104" ht="17.25" customHeight="1"/>
+    <row r="105" ht="17.25" customHeight="1"/>
+    <row r="106" ht="17.25" customHeight="1"/>
+    <row r="107" ht="17.25" customHeight="1"/>
+    <row r="108" ht="17.25" customHeight="1"/>
+    <row r="109" ht="17.25" customHeight="1"/>
+    <row r="110" ht="17.25" customHeight="1"/>
+    <row r="111" ht="17.25" customHeight="1"/>
+    <row r="112" ht="17.25" customHeight="1"/>
+    <row r="113" ht="17.25" customHeight="1"/>
+    <row r="114" ht="17.25" customHeight="1"/>
+    <row r="115" ht="17.25" customHeight="1"/>
+    <row r="116" ht="17.25" customHeight="1"/>
+    <row r="117" ht="17.25" customHeight="1"/>
+    <row r="118" ht="17.25" customHeight="1"/>
+    <row r="119" ht="17.25" customHeight="1"/>
+    <row r="120" ht="17.25" customHeight="1"/>
+    <row r="121" ht="17.25" customHeight="1"/>
+    <row r="122" ht="17.25" customHeight="1"/>
+    <row r="123" ht="17.25" customHeight="1"/>
+    <row r="124" ht="17.25" customHeight="1"/>
+    <row r="125" ht="17.25" customHeight="1"/>
+    <row r="126" ht="17.25" customHeight="1"/>
+    <row r="127" ht="17.25" customHeight="1"/>
+    <row r="128" ht="17.25" customHeight="1"/>
+    <row r="129" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1"/>
+    <row r="131" ht="17.25" customHeight="1"/>
+    <row r="132" ht="17.25" customHeight="1"/>
+    <row r="133" ht="17.25" customHeight="1"/>
+    <row r="134" ht="17.25" customHeight="1"/>
+    <row r="135" ht="17.25" customHeight="1"/>
+    <row r="136" ht="17.25" customHeight="1"/>
+    <row r="137" ht="17.25" customHeight="1"/>
+    <row r="138" ht="17.25" customHeight="1"/>
+    <row r="139" ht="17.25" customHeight="1"/>
+    <row r="140" ht="17.25" customHeight="1"/>
+    <row r="141" ht="17.25" customHeight="1"/>
+    <row r="142" ht="17.25" customHeight="1"/>
+    <row r="143" ht="17.25" customHeight="1"/>
+    <row r="144" ht="17.25" customHeight="1"/>
+    <row r="145" ht="17.25" customHeight="1"/>
+    <row r="146" ht="17.25" customHeight="1"/>
+    <row r="147" ht="17.25" customHeight="1"/>
+    <row r="148" ht="17.25" customHeight="1"/>
+    <row r="149" ht="17.25" customHeight="1"/>
+    <row r="150" ht="17.25" customHeight="1"/>
+    <row r="151" ht="17.25" customHeight="1"/>
+    <row r="152" ht="17.25" customHeight="1"/>
+    <row r="153" ht="17.25" customHeight="1"/>
+    <row r="154" ht="17.25" customHeight="1"/>
+    <row r="155" ht="17.25" customHeight="1"/>
+    <row r="156" ht="17.25" customHeight="1"/>
+    <row r="157" ht="17.25" customHeight="1"/>
+    <row r="158" ht="17.25" customHeight="1"/>
+    <row r="159" ht="17.25" customHeight="1"/>
+    <row r="160" ht="17.25" customHeight="1"/>
+    <row r="161" ht="17.25" customHeight="1"/>
+    <row r="162" ht="17.25" customHeight="1"/>
+    <row r="163" ht="17.25" customHeight="1"/>
+    <row r="164" ht="17.25" customHeight="1"/>
+    <row r="165" ht="17.25" customHeight="1"/>
+    <row r="166" ht="17.25" customHeight="1"/>
+    <row r="167" ht="17.25" customHeight="1"/>
+    <row r="168" ht="17.25" customHeight="1"/>
+    <row r="169" ht="17.25" customHeight="1"/>
+    <row r="170" ht="17.25" customHeight="1"/>
+    <row r="171" ht="17.25" customHeight="1"/>
+    <row r="172" ht="17.25" customHeight="1"/>
+    <row r="173" ht="17.25" customHeight="1"/>
+    <row r="174" ht="17.25" customHeight="1"/>
+    <row r="175" ht="17.25" customHeight="1"/>
+    <row r="176" ht="17.25" customHeight="1"/>
+    <row r="177" ht="17.25" customHeight="1"/>
+    <row r="178" ht="17.25" customHeight="1"/>
+    <row r="179" ht="17.25" customHeight="1"/>
+    <row r="180" ht="17.25" customHeight="1"/>
+    <row r="181" ht="17.25" customHeight="1"/>
+    <row r="182" ht="17.25" customHeight="1"/>
+    <row r="183" ht="17.25" customHeight="1"/>
+    <row r="184" ht="17.25" customHeight="1"/>
+    <row r="185" ht="17.25" customHeight="1"/>
+    <row r="186" ht="17.25" customHeight="1"/>
+    <row r="187" ht="17.25" customHeight="1"/>
+    <row r="188" ht="17.25" customHeight="1"/>
+    <row r="189" ht="17.25" customHeight="1"/>
+    <row r="190" ht="17.25" customHeight="1"/>
+    <row r="191" ht="17.25" customHeight="1"/>
+    <row r="192" ht="17.25" customHeight="1"/>
+    <row r="193" ht="17.25" customHeight="1"/>
+    <row r="194" ht="17.25" customHeight="1"/>
+    <row r="195" ht="17.25" customHeight="1"/>
+    <row r="196" ht="17.25" customHeight="1"/>
+    <row r="197" ht="17.25" customHeight="1"/>
+    <row r="198" ht="17.25" customHeight="1"/>
+    <row r="199" ht="17.25" customHeight="1"/>
+    <row r="200" ht="17.25" customHeight="1"/>
+    <row r="201" ht="17.25" customHeight="1"/>
+    <row r="202" ht="17.25" customHeight="1"/>
+    <row r="203" ht="17.25" customHeight="1"/>
+    <row r="204" ht="17.25" customHeight="1"/>
+    <row r="205" ht="17.25" customHeight="1"/>
+    <row r="206" ht="17.25" customHeight="1"/>
+    <row r="207" ht="17.25" customHeight="1"/>
+    <row r="208" ht="17.25" customHeight="1"/>
+    <row r="209" ht="17.25" customHeight="1"/>
+    <row r="210" ht="17.25" customHeight="1"/>
+    <row r="211" ht="17.25" customHeight="1"/>
+    <row r="212" ht="17.25" customHeight="1"/>
+    <row r="213" ht="17.25" customHeight="1"/>
+    <row r="214" ht="17.25" customHeight="1"/>
+    <row r="215" ht="17.25" customHeight="1"/>
+    <row r="216" ht="17.25" customHeight="1"/>
+    <row r="217" ht="17.25" customHeight="1"/>
+    <row r="218" ht="17.25" customHeight="1"/>
+    <row r="219" ht="17.25" customHeight="1"/>
+    <row r="220" ht="17.25" customHeight="1"/>
+    <row r="221" ht="17.25" customHeight="1"/>
+    <row r="222" ht="17.25" customHeight="1"/>
+    <row r="223" ht="17.25" customHeight="1"/>
+    <row r="224" ht="17.25" customHeight="1"/>
+    <row r="225" ht="17.25" customHeight="1"/>
+    <row r="226" ht="17.25" customHeight="1"/>
+    <row r="227" ht="17.25" customHeight="1"/>
+    <row r="228" ht="17.25" customHeight="1"/>
+    <row r="229" ht="17.25" customHeight="1"/>
+    <row r="230" ht="17.25" customHeight="1"/>
+    <row r="231" ht="17.25" customHeight="1"/>
+    <row r="232" ht="17.25" customHeight="1"/>
+    <row r="233" ht="17.25" customHeight="1"/>
+    <row r="234" ht="17.25" customHeight="1"/>
+    <row r="235" ht="17.25" customHeight="1"/>
+    <row r="236" ht="17.25" customHeight="1"/>
+    <row r="237" ht="17.25" customHeight="1"/>
+    <row r="238" ht="17.25" customHeight="1"/>
+    <row r="239" ht="17.25" customHeight="1"/>
+    <row r="240" ht="17.25" customHeight="1"/>
+    <row r="241" ht="17.25" customHeight="1"/>
+    <row r="242" ht="17.25" customHeight="1"/>
+    <row r="243" ht="17.25" customHeight="1"/>
+    <row r="244" ht="17.25" customHeight="1"/>
+    <row r="245" ht="17.25" customHeight="1"/>
+    <row r="246" ht="17.25" customHeight="1"/>
+    <row r="247" ht="17.25" customHeight="1"/>
+    <row r="248" ht="17.25" customHeight="1"/>
+    <row r="249" ht="17.25" customHeight="1"/>
+    <row r="250" ht="17.25" customHeight="1"/>
+    <row r="251" ht="17.25" customHeight="1"/>
+    <row r="252" ht="17.25" customHeight="1"/>
+    <row r="253" ht="17.25" customHeight="1"/>
+    <row r="254" ht="17.25" customHeight="1"/>
+    <row r="255" ht="17.25" customHeight="1"/>
+    <row r="256" ht="17.25" customHeight="1"/>
+    <row r="257" ht="17.25" customHeight="1"/>
+    <row r="258" ht="17.25" customHeight="1"/>
+    <row r="259" ht="17.25" customHeight="1"/>
+    <row r="260" ht="17.25" customHeight="1"/>
+    <row r="261" ht="17.25" customHeight="1"/>
+    <row r="262" ht="17.25" customHeight="1"/>
+    <row r="263" ht="17.25" customHeight="1"/>
+    <row r="264" ht="17.25" customHeight="1"/>
+    <row r="265" ht="17.25" customHeight="1"/>
+    <row r="266" ht="17.25" customHeight="1"/>
+    <row r="267" ht="17.25" customHeight="1"/>
+    <row r="268" ht="17.25" customHeight="1"/>
+    <row r="269" ht="17.25" customHeight="1"/>
+    <row r="270" ht="17.25" customHeight="1"/>
+    <row r="271" ht="17.25" customHeight="1"/>
+    <row r="272" ht="17.25" customHeight="1"/>
+    <row r="273" ht="17.25" customHeight="1"/>
+    <row r="274" ht="17.25" customHeight="1"/>
+    <row r="275" ht="17.25" customHeight="1"/>
+    <row r="276" ht="17.25" customHeight="1"/>
+    <row r="277" ht="17.25" customHeight="1"/>
+    <row r="278" ht="17.25" customHeight="1"/>
+    <row r="279" ht="17.25" customHeight="1"/>
+    <row r="280" ht="17.25" customHeight="1"/>
+    <row r="281" ht="17.25" customHeight="1"/>
+    <row r="282" ht="17.25" customHeight="1"/>
+    <row r="283" ht="17.25" customHeight="1"/>
+    <row r="284" ht="17.25" customHeight="1"/>
+    <row r="285" ht="17.25" customHeight="1"/>
+    <row r="286" ht="17.25" customHeight="1"/>
+    <row r="287" ht="17.25" customHeight="1"/>
+    <row r="288" ht="17.25" customHeight="1"/>
+    <row r="289" ht="17.25" customHeight="1"/>
+    <row r="290" ht="17.25" customHeight="1"/>
+    <row r="291" ht="17.25" customHeight="1"/>
+    <row r="292" ht="17.25" customHeight="1"/>
+    <row r="293" ht="17.25" customHeight="1"/>
+    <row r="294" ht="17.25" customHeight="1"/>
+    <row r="295" ht="17.25" customHeight="1"/>
+    <row r="296" ht="17.25" customHeight="1"/>
+    <row r="297" ht="17.25" customHeight="1"/>
+    <row r="298" ht="17.25" customHeight="1"/>
+    <row r="299" ht="17.25" customHeight="1"/>
+    <row r="300" ht="17.25" customHeight="1"/>
+    <row r="301" ht="17.25" customHeight="1"/>
+    <row r="302" ht="17.25" customHeight="1"/>
+    <row r="303" ht="17.25" customHeight="1"/>
+    <row r="304" ht="17.25" customHeight="1"/>
+    <row r="305" ht="17.25" customHeight="1"/>
+    <row r="306" ht="17.25" customHeight="1"/>
+    <row r="307" ht="17.25" customHeight="1"/>
+    <row r="308" ht="17.25" customHeight="1"/>
+    <row r="309" ht="17.25" customHeight="1"/>
+    <row r="310" ht="17.25" customHeight="1"/>
+    <row r="311" ht="17.25" customHeight="1"/>
+    <row r="312" ht="17.25" customHeight="1"/>
+    <row r="313" ht="17.25" customHeight="1"/>
+    <row r="314" ht="17.25" customHeight="1"/>
+    <row r="315" ht="17.25" customHeight="1"/>
+    <row r="316" ht="17.25" customHeight="1"/>
+    <row r="317" ht="17.25" customHeight="1"/>
+    <row r="318" ht="17.25" customHeight="1"/>
+    <row r="319" ht="17.25" customHeight="1"/>
+    <row r="320" ht="17.25" customHeight="1"/>
+    <row r="321" ht="17.25" customHeight="1"/>
+    <row r="322" ht="17.25" customHeight="1"/>
+    <row r="323" ht="17.25" customHeight="1"/>
+    <row r="324" ht="17.25" customHeight="1"/>
+    <row r="325" ht="17.25" customHeight="1"/>
+    <row r="326" ht="17.25" customHeight="1"/>
+    <row r="327" ht="17.25" customHeight="1"/>
+    <row r="328" ht="17.25" customHeight="1"/>
+    <row r="329" ht="17.25" customHeight="1"/>
+    <row r="330" ht="17.25" customHeight="1"/>
+    <row r="331" ht="17.25" customHeight="1"/>
+    <row r="332" ht="17.25" customHeight="1"/>
+    <row r="333" ht="17.25" customHeight="1"/>
+    <row r="334" ht="17.25" customHeight="1"/>
+    <row r="335" ht="17.25" customHeight="1"/>
+    <row r="336" ht="17.25" customHeight="1"/>
+    <row r="337" ht="17.25" customHeight="1"/>
+    <row r="338" ht="17.25" customHeight="1"/>
+    <row r="339" ht="17.25" customHeight="1"/>
+    <row r="340" ht="17.25" customHeight="1"/>
+    <row r="341" ht="17.25" customHeight="1"/>
+    <row r="342" ht="17.25" customHeight="1"/>
+    <row r="343" ht="17.25" customHeight="1"/>
+    <row r="344" ht="17.25" customHeight="1"/>
+    <row r="345" ht="17.25" customHeight="1"/>
+    <row r="346" ht="17.25" customHeight="1"/>
+    <row r="347" ht="17.25" customHeight="1"/>
+    <row r="348" ht="17.25" customHeight="1"/>
+    <row r="349" ht="17.25" customHeight="1"/>
+    <row r="350" ht="17.25" customHeight="1"/>
+    <row r="351" ht="17.25" customHeight="1"/>
+    <row r="352" ht="17.25" customHeight="1"/>
+    <row r="353" ht="17.25" customHeight="1"/>
+    <row r="354" ht="17.25" customHeight="1"/>
+    <row r="355" ht="17.25" customHeight="1"/>
+    <row r="356" ht="17.25" customHeight="1"/>
+    <row r="357" ht="17.25" customHeight="1"/>
+    <row r="358" ht="17.25" customHeight="1"/>
+    <row r="359" ht="17.25" customHeight="1"/>
+    <row r="360" ht="17.25" customHeight="1"/>
+    <row r="361" ht="17.25" customHeight="1"/>
+    <row r="362" ht="17.25" customHeight="1"/>
+    <row r="363" ht="17.25" customHeight="1"/>
+    <row r="364" ht="17.25" customHeight="1"/>
+    <row r="365" ht="17.25" customHeight="1"/>
+    <row r="366" ht="17.25" customHeight="1"/>
+    <row r="367" ht="17.25" customHeight="1"/>
+    <row r="368" ht="17.25" customHeight="1"/>
+    <row r="369" ht="17.25" customHeight="1"/>
+    <row r="370" ht="17.25" customHeight="1"/>
+    <row r="371" ht="17.25" customHeight="1"/>
+    <row r="372" ht="17.25" customHeight="1"/>
+    <row r="373" ht="17.25" customHeight="1"/>
+    <row r="374" ht="17.25" customHeight="1"/>
+    <row r="375" ht="17.25" customHeight="1"/>
+    <row r="376" ht="17.25" customHeight="1"/>
+    <row r="377" ht="17.25" customHeight="1"/>
+    <row r="378" ht="17.25" customHeight="1"/>
+    <row r="379" ht="17.25" customHeight="1"/>
+    <row r="380" ht="17.25" customHeight="1"/>
+    <row r="381" ht="17.25" customHeight="1"/>
+    <row r="382" ht="17.25" customHeight="1"/>
+    <row r="383" ht="17.25" customHeight="1"/>
+    <row r="384" ht="17.25" customHeight="1"/>
+    <row r="385" ht="17.25" customHeight="1"/>
+    <row r="386" ht="17.25" customHeight="1"/>
+    <row r="387" ht="17.25" customHeight="1"/>
+    <row r="388" ht="17.25" customHeight="1"/>
+    <row r="389" ht="17.25" customHeight="1"/>
+    <row r="390" ht="17.25" customHeight="1"/>
+    <row r="391" ht="17.25" customHeight="1"/>
+    <row r="392" ht="17.25" customHeight="1"/>
+    <row r="393" ht="17.25" customHeight="1"/>
+    <row r="394" ht="17.25" customHeight="1"/>
+    <row r="395" ht="17.25" customHeight="1"/>
+    <row r="396" ht="17.25" customHeight="1"/>
+    <row r="397" ht="17.25" customHeight="1"/>
+    <row r="398" ht="17.25" customHeight="1"/>
+    <row r="399" ht="17.25" customHeight="1"/>
+    <row r="400" ht="17.25" customHeight="1"/>
+    <row r="401" ht="17.25" customHeight="1"/>
+    <row r="402" ht="17.25" customHeight="1"/>
+    <row r="403" ht="17.25" customHeight="1"/>
+    <row r="404" ht="17.25" customHeight="1"/>
+    <row r="405" ht="17.25" customHeight="1"/>
+    <row r="406" ht="17.25" customHeight="1"/>
+    <row r="407" ht="17.25" customHeight="1"/>
+    <row r="408" ht="17.25" customHeight="1"/>
+    <row r="409" ht="17.25" customHeight="1"/>
+    <row r="410" ht="17.25" customHeight="1"/>
+    <row r="411" ht="17.25" customHeight="1"/>
+    <row r="412" ht="17.25" customHeight="1"/>
+    <row r="413" ht="17.25" customHeight="1"/>
+    <row r="414" ht="17.25" customHeight="1"/>
+    <row r="415" ht="17.25" customHeight="1"/>
+    <row r="416" ht="17.25" customHeight="1"/>
+    <row r="417" ht="17.25" customHeight="1"/>
+    <row r="418" ht="17.25" customHeight="1"/>
+    <row r="419" ht="17.25" customHeight="1"/>
+    <row r="420" ht="17.25" customHeight="1"/>
+    <row r="421" ht="17.25" customHeight="1"/>
+    <row r="422" ht="17.25" customHeight="1"/>
+    <row r="423" ht="17.25" customHeight="1"/>
+    <row r="424" ht="17.25" customHeight="1"/>
+    <row r="425" ht="17.25" customHeight="1"/>
+    <row r="426" ht="17.25" customHeight="1"/>
+    <row r="427" ht="17.25" customHeight="1"/>
+    <row r="428" ht="17.25" customHeight="1"/>
+    <row r="429" ht="17.25" customHeight="1"/>
+    <row r="430" ht="17.25" customHeight="1"/>
+    <row r="431" ht="17.25" customHeight="1"/>
+    <row r="432" ht="17.25" customHeight="1"/>
+    <row r="433" ht="17.25" customHeight="1"/>
+    <row r="434" ht="17.25" customHeight="1"/>
+    <row r="435" ht="17.25" customHeight="1"/>
+    <row r="436" ht="17.25" customHeight="1"/>
+    <row r="437" ht="17.25" customHeight="1"/>
+    <row r="438" ht="17.25" customHeight="1"/>
+    <row r="439" ht="17.25" customHeight="1"/>
+    <row r="440" ht="17.25" customHeight="1"/>
+    <row r="441" ht="17.25" customHeight="1"/>
+    <row r="442" ht="17.25" customHeight="1"/>
+    <row r="443" ht="17.25" customHeight="1"/>
+    <row r="444" ht="17.25" customHeight="1"/>
+    <row r="445" ht="17.25" customHeight="1"/>
+    <row r="446" ht="17.25" customHeight="1"/>
+    <row r="447" ht="17.25" customHeight="1"/>
+    <row r="448" ht="17.25" customHeight="1"/>
+    <row r="449" ht="17.25" customHeight="1"/>
+    <row r="450" ht="17.25" customHeight="1"/>
+    <row r="451" ht="17.25" customHeight="1"/>
+    <row r="452" ht="17.25" customHeight="1"/>
+    <row r="453" ht="17.25" customHeight="1"/>
+    <row r="454" ht="17.25" customHeight="1"/>
+    <row r="455" ht="17.25" customHeight="1"/>
+    <row r="456" ht="17.25" customHeight="1"/>
+    <row r="457" ht="17.25" customHeight="1"/>
+    <row r="458" ht="17.25" customHeight="1"/>
+    <row r="459" ht="17.25" customHeight="1"/>
+    <row r="460" ht="17.25" customHeight="1"/>
+    <row r="461" ht="17.25" customHeight="1"/>
+    <row r="462" ht="17.25" customHeight="1"/>
+    <row r="463" ht="17.25" customHeight="1"/>
+    <row r="464" ht="17.25" customHeight="1"/>
+    <row r="465" ht="17.25" customHeight="1"/>
+    <row r="466" ht="17.25" customHeight="1"/>
+    <row r="467" ht="17.25" customHeight="1"/>
+    <row r="468" ht="17.25" customHeight="1"/>
+    <row r="469" ht="17.25" customHeight="1"/>
+    <row r="470" ht="17.25" customHeight="1"/>
+    <row r="471" ht="17.25" customHeight="1"/>
+    <row r="472" ht="17.25" customHeight="1"/>
+    <row r="473" ht="17.25" customHeight="1"/>
+    <row r="474" ht="17.25" customHeight="1"/>
+    <row r="475" ht="17.25" customHeight="1"/>
+    <row r="476" ht="17.25" customHeight="1"/>
+    <row r="477" ht="17.25" customHeight="1"/>
+    <row r="478" ht="17.25" customHeight="1"/>
+    <row r="479" ht="17.25" customHeight="1"/>
+    <row r="480" ht="17.25" customHeight="1"/>
+    <row r="481" ht="17.25" customHeight="1"/>
+    <row r="482" ht="17.25" customHeight="1"/>
+    <row r="483" ht="17.25" customHeight="1"/>
+    <row r="484" ht="17.25" customHeight="1"/>
+    <row r="485" ht="17.25" customHeight="1"/>
+    <row r="486" ht="17.25" customHeight="1"/>
+    <row r="487" ht="17.25" customHeight="1"/>
+    <row r="488" ht="17.25" customHeight="1"/>
+    <row r="489" ht="17.25" customHeight="1"/>
+    <row r="490" ht="17.25" customHeight="1"/>
+    <row r="491" ht="17.25" customHeight="1"/>
+    <row r="492" ht="17.25" customHeight="1"/>
+    <row r="493" ht="17.25" customHeight="1"/>
+    <row r="494" ht="17.25" customHeight="1"/>
+    <row r="495" ht="17.25" customHeight="1"/>
+    <row r="496" ht="17.25" customHeight="1"/>
+    <row r="497" ht="17.25" customHeight="1"/>
+    <row r="498" ht="17.25" customHeight="1"/>
+    <row r="499" ht="17.25" customHeight="1"/>
+    <row r="500" ht="17.25" customHeight="1"/>
+    <row r="501" ht="17.25" customHeight="1"/>
+    <row r="502" ht="17.25" customHeight="1"/>
+    <row r="503" ht="17.25" customHeight="1"/>
+    <row r="504" ht="17.25" customHeight="1"/>
+    <row r="505" ht="17.25" customHeight="1"/>
+    <row r="506" ht="17.25" customHeight="1"/>
+    <row r="507" ht="17.25" customHeight="1"/>
+    <row r="508" ht="17.25" customHeight="1"/>
+    <row r="509" ht="17.25" customHeight="1"/>
+    <row r="510" ht="17.25" customHeight="1"/>
+    <row r="511" ht="17.25" customHeight="1"/>
+    <row r="512" ht="17.25" customHeight="1"/>
+    <row r="513" ht="17.25" customHeight="1"/>
+    <row r="514" ht="17.25" customHeight="1"/>
+    <row r="515" ht="17.25" customHeight="1"/>
+    <row r="516" ht="17.25" customHeight="1"/>
+    <row r="517" ht="17.25" customHeight="1"/>
+    <row r="518" ht="17.25" customHeight="1"/>
+    <row r="519" ht="17.25" customHeight="1"/>
+    <row r="520" ht="17.25" customHeight="1"/>
+    <row r="521" ht="17.25" customHeight="1"/>
+    <row r="522" ht="17.25" customHeight="1"/>
+    <row r="523" ht="17.25" customHeight="1"/>
+    <row r="524" ht="17.25" customHeight="1"/>
+    <row r="525" ht="17.25" customHeight="1"/>
+    <row r="526" ht="17.25" customHeight="1"/>
+    <row r="527" ht="17.25" customHeight="1"/>
+    <row r="528" ht="17.25" customHeight="1"/>
+    <row r="529" ht="17.25" customHeight="1"/>
+    <row r="530" ht="17.25" customHeight="1"/>
+    <row r="531" ht="17.25" customHeight="1"/>
+    <row r="532" ht="17.25" customHeight="1"/>
+    <row r="533" ht="17.25" customHeight="1"/>
+    <row r="534" ht="17.25" customHeight="1"/>
+    <row r="535" ht="17.25" customHeight="1"/>
+    <row r="536" ht="17.25" customHeight="1"/>
+    <row r="537" ht="17.25" customHeight="1"/>
+    <row r="538" ht="17.25" customHeight="1"/>
+    <row r="539" ht="17.25" customHeight="1"/>
+    <row r="540" ht="17.25" customHeight="1"/>
+    <row r="541" ht="17.25" customHeight="1"/>
+    <row r="542" ht="17.25" customHeight="1"/>
+    <row r="543" ht="17.25" customHeight="1"/>
+    <row r="544" ht="17.25" customHeight="1"/>
+    <row r="545" ht="17.25" customHeight="1"/>
+    <row r="546" ht="17.25" customHeight="1"/>
+    <row r="547" ht="17.25" customHeight="1"/>
+    <row r="548" ht="17.25" customHeight="1"/>
+    <row r="549" ht="17.25" customHeight="1"/>
+    <row r="550" ht="17.25" customHeight="1"/>
+    <row r="551" ht="17.25" customHeight="1"/>
+    <row r="552" ht="17.25" customHeight="1"/>
+    <row r="553" ht="17.25" customHeight="1"/>
+    <row r="554" ht="17.25" customHeight="1"/>
+    <row r="555" ht="17.25" customHeight="1"/>
+    <row r="556" ht="17.25" customHeight="1"/>
+    <row r="557" ht="17.25" customHeight="1"/>
+    <row r="558" ht="17.25" customHeight="1"/>
+    <row r="559" ht="17.25" customHeight="1"/>
+    <row r="560" ht="17.25" customHeight="1"/>
+    <row r="561" ht="17.25" customHeight="1"/>
+    <row r="562" ht="17.25" customHeight="1"/>
+    <row r="563" ht="17.25" customHeight="1"/>
+    <row r="564" ht="17.25" customHeight="1"/>
+    <row r="565" ht="17.25" customHeight="1"/>
+    <row r="566" ht="17.25" customHeight="1"/>
+    <row r="567" ht="17.25" customHeight="1"/>
+    <row r="568" ht="17.25" customHeight="1"/>
+    <row r="569" ht="17.25" customHeight="1"/>
+    <row r="570" ht="17.25" customHeight="1"/>
+    <row r="571" ht="17.25" customHeight="1"/>
+    <row r="572" ht="17.25" customHeight="1"/>
+    <row r="573" ht="17.25" customHeight="1"/>
+    <row r="574" ht="17.25" customHeight="1"/>
+    <row r="575" ht="17.25" customHeight="1"/>
+    <row r="576" ht="17.25" customHeight="1"/>
+    <row r="577" ht="17.25" customHeight="1"/>
+    <row r="578" ht="17.25" customHeight="1"/>
+    <row r="579" ht="17.25" customHeight="1"/>
+    <row r="580" ht="17.25" customHeight="1"/>
+    <row r="581" ht="17.25" customHeight="1"/>
+    <row r="582" ht="17.25" customHeight="1"/>
+    <row r="583" ht="17.25" customHeight="1"/>
+    <row r="584" ht="17.25" customHeight="1"/>
+    <row r="585" ht="17.25" customHeight="1"/>
+    <row r="586" ht="17.25" customHeight="1"/>
+    <row r="587" ht="17.25" customHeight="1"/>
+    <row r="588" ht="17.25" customHeight="1"/>
+    <row r="589" ht="17.25" customHeight="1"/>
+    <row r="590" ht="17.25" customHeight="1"/>
+    <row r="591" ht="17.25" customHeight="1"/>
+    <row r="592" ht="17.25" customHeight="1"/>
+    <row r="593" ht="17.25" customHeight="1"/>
+    <row r="594" ht="17.25" customHeight="1"/>
+    <row r="595" ht="17.25" customHeight="1"/>
+    <row r="596" ht="17.25" customHeight="1"/>
+    <row r="597" ht="17.25" customHeight="1"/>
+    <row r="598" ht="17.25" customHeight="1"/>
+    <row r="599" ht="17.25" customHeight="1"/>
+    <row r="600" ht="17.25" customHeight="1"/>
+    <row r="601" ht="17.25" customHeight="1"/>
+    <row r="602" ht="17.25" customHeight="1"/>
+    <row r="603" ht="17.25" customHeight="1"/>
+    <row r="604" ht="17.25" customHeight="1"/>
+    <row r="605" ht="17.25" customHeight="1"/>
+    <row r="606" ht="17.25" customHeight="1"/>
+    <row r="607" ht="17.25" customHeight="1"/>
+    <row r="608" ht="17.25" customHeight="1"/>
+    <row r="609" ht="17.25" customHeight="1"/>
+    <row r="610" ht="17.25" customHeight="1"/>
+    <row r="611" ht="17.25" customHeight="1"/>
+    <row r="612" ht="17.25" customHeight="1"/>
+    <row r="613" ht="17.25" customHeight="1"/>
+    <row r="614" ht="17.25" customHeight="1"/>
+    <row r="615" ht="17.25" customHeight="1"/>
+    <row r="616" ht="17.25" customHeight="1"/>
+    <row r="617" ht="17.25" customHeight="1"/>
+    <row r="618" ht="17.25" customHeight="1"/>
+    <row r="619" ht="17.25" customHeight="1"/>
+    <row r="620" ht="17.25" customHeight="1"/>
+    <row r="621" ht="17.25" customHeight="1"/>
+    <row r="622" ht="17.25" customHeight="1"/>
+    <row r="623" ht="17.25" customHeight="1"/>
+    <row r="624" ht="17.25" customHeight="1"/>
+    <row r="625" ht="17.25" customHeight="1"/>
+    <row r="626" ht="17.25" customHeight="1"/>
+    <row r="627" ht="17.25" customHeight="1"/>
+    <row r="628" ht="17.25" customHeight="1"/>
+    <row r="629" ht="17.25" customHeight="1"/>
+    <row r="630" ht="17.25" customHeight="1"/>
+    <row r="631" ht="17.25" customHeight="1"/>
+    <row r="632" ht="17.25" customHeight="1"/>
+    <row r="633" ht="17.25" customHeight="1"/>
+    <row r="634" ht="17.25" customHeight="1"/>
+    <row r="635" ht="17.25" customHeight="1"/>
+    <row r="636" ht="17.25" customHeight="1"/>
+    <row r="637" ht="17.25" customHeight="1"/>
+    <row r="638" ht="17.25" customHeight="1"/>
+    <row r="639" ht="17.25" customHeight="1"/>
+    <row r="640" ht="17.25" customHeight="1"/>
+    <row r="641" ht="17.25" customHeight="1"/>
+    <row r="642" ht="17.25" customHeight="1"/>
+    <row r="643" ht="17.25" customHeight="1"/>
+    <row r="644" ht="17.25" customHeight="1"/>
+    <row r="645" ht="17.25" customHeight="1"/>
+    <row r="646" ht="17.25" customHeight="1"/>
+    <row r="647" ht="17.25" customHeight="1"/>
+    <row r="648" ht="17.25" customHeight="1"/>
+    <row r="649" ht="17.25" customHeight="1"/>
+    <row r="650" ht="17.25" customHeight="1"/>
+    <row r="651" ht="17.25" customHeight="1"/>
+    <row r="652" ht="17.25" customHeight="1"/>
+    <row r="653" ht="17.25" customHeight="1"/>
+    <row r="654" ht="17.25" customHeight="1"/>
+    <row r="655" ht="17.25" customHeight="1"/>
+    <row r="656" ht="17.25" customHeight="1"/>
+    <row r="657" ht="17.25" customHeight="1"/>
+    <row r="658" ht="17.25" customHeight="1"/>
+    <row r="659" ht="17.25" customHeight="1"/>
+    <row r="660" ht="17.25" customHeight="1"/>
+    <row r="661" ht="17.25" customHeight="1"/>
+    <row r="662" ht="17.25" customHeight="1"/>
+    <row r="663" ht="17.25" customHeight="1"/>
+    <row r="664" ht="17.25" customHeight="1"/>
+    <row r="665" ht="17.25" customHeight="1"/>
+    <row r="666" ht="17.25" customHeight="1"/>
+    <row r="667" ht="17.25" customHeight="1"/>
+    <row r="668" ht="17.25" customHeight="1"/>
+    <row r="669" ht="17.25" customHeight="1"/>
+    <row r="670" ht="17.25" customHeight="1"/>
+    <row r="671" ht="17.25" customHeight="1"/>
+    <row r="672" ht="17.25" customHeight="1"/>
+    <row r="673" ht="17.25" customHeight="1"/>
+    <row r="674" ht="17.25" customHeight="1"/>
+    <row r="675" ht="17.25" customHeight="1"/>
+    <row r="676" ht="17.25" customHeight="1"/>
+    <row r="677" ht="17.25" customHeight="1"/>
+    <row r="678" ht="17.25" customHeight="1"/>
+    <row r="679" ht="17.25" customHeight="1"/>
+    <row r="680" ht="17.25" customHeight="1"/>
+    <row r="681" ht="17.25" customHeight="1"/>
+    <row r="682" ht="17.25" customHeight="1"/>
+    <row r="683" ht="17.25" customHeight="1"/>
+    <row r="684" ht="17.25" customHeight="1"/>
+    <row r="685" ht="17.25" customHeight="1"/>
+    <row r="686" ht="17.25" customHeight="1"/>
+    <row r="687" ht="17.25" customHeight="1"/>
+    <row r="688" ht="17.25" customHeight="1"/>
+    <row r="689" ht="17.25" customHeight="1"/>
+    <row r="690" ht="17.25" customHeight="1"/>
+    <row r="691" ht="17.25" customHeight="1"/>
+    <row r="692" ht="17.25" customHeight="1"/>
+    <row r="693" ht="17.25" customHeight="1"/>
+    <row r="694" ht="17.25" customHeight="1"/>
+    <row r="695" ht="17.25" customHeight="1"/>
+    <row r="696" ht="17.25" customHeight="1"/>
+    <row r="697" ht="17.25" customHeight="1"/>
+    <row r="698" ht="17.25" customHeight="1"/>
+    <row r="699" ht="17.25" customHeight="1"/>
+    <row r="700" ht="17.25" customHeight="1"/>
+    <row r="701" ht="17.25" customHeight="1"/>
+    <row r="702" ht="17.25" customHeight="1"/>
+    <row r="703" ht="17.25" customHeight="1"/>
+    <row r="704" ht="17.25" customHeight="1"/>
+    <row r="705" ht="17.25" customHeight="1"/>
+    <row r="706" ht="17.25" customHeight="1"/>
+    <row r="707" ht="17.25" customHeight="1"/>
+    <row r="708" ht="17.25" customHeight="1"/>
+    <row r="709" ht="17.25" customHeight="1"/>
+    <row r="710" ht="17.25" customHeight="1"/>
+    <row r="711" ht="17.25" customHeight="1"/>
+    <row r="712" ht="17.25" customHeight="1"/>
+    <row r="713" ht="17.25" customHeight="1"/>
+    <row r="714" ht="17.25" customHeight="1"/>
+    <row r="715" ht="17.25" customHeight="1"/>
+    <row r="716" ht="17.25" customHeight="1"/>
+    <row r="717" ht="17.25" customHeight="1"/>
+    <row r="718" ht="17.25" customHeight="1"/>
+    <row r="719" ht="17.25" customHeight="1"/>
+    <row r="720" ht="17.25" customHeight="1"/>
+    <row r="721" ht="17.25" customHeight="1"/>
+    <row r="722" ht="17.25" customHeight="1"/>
+    <row r="723" ht="17.25" customHeight="1"/>
+    <row r="724" ht="17.25" customHeight="1"/>
+    <row r="725" ht="17.25" customHeight="1"/>
+    <row r="726" ht="17.25" customHeight="1"/>
+    <row r="727" ht="17.25" customHeight="1"/>
+    <row r="728" ht="17.25" customHeight="1"/>
+    <row r="729" ht="17.25" customHeight="1"/>
+    <row r="730" ht="17.25" customHeight="1"/>
+    <row r="731" ht="17.25" customHeight="1"/>
+    <row r="732" ht="17.25" customHeight="1"/>
+    <row r="733" ht="17.25" customHeight="1"/>
+    <row r="734" ht="17.25" customHeight="1"/>
+    <row r="735" ht="17.25" customHeight="1"/>
+    <row r="736" ht="17.25" customHeight="1"/>
+    <row r="737" ht="17.25" customHeight="1"/>
+    <row r="738" ht="17.25" customHeight="1"/>
+    <row r="739" ht="17.25" customHeight="1"/>
+    <row r="740" ht="17.25" customHeight="1"/>
+    <row r="741" ht="17.25" customHeight="1"/>
+    <row r="742" ht="17.25" customHeight="1"/>
+    <row r="743" ht="17.25" customHeight="1"/>
+    <row r="744" ht="17.25" customHeight="1"/>
+    <row r="745" ht="17.25" customHeight="1"/>
+    <row r="746" ht="17.25" customHeight="1"/>
+    <row r="747" ht="17.25" customHeight="1"/>
+    <row r="748" ht="17.25" customHeight="1"/>
+    <row r="749" ht="17.25" customHeight="1"/>
+    <row r="750" ht="17.25" customHeight="1"/>
+    <row r="751" ht="17.25" customHeight="1"/>
+    <row r="752" ht="17.25" customHeight="1"/>
+    <row r="753" ht="17.25" customHeight="1"/>
+    <row r="754" ht="17.25" customHeight="1"/>
+    <row r="755" ht="17.25" customHeight="1"/>
+    <row r="756" ht="17.25" customHeight="1"/>
+    <row r="757" ht="17.25" customHeight="1"/>
+    <row r="758" ht="17.25" customHeight="1"/>
+    <row r="759" ht="17.25" customHeight="1"/>
+    <row r="760" ht="17.25" customHeight="1"/>
+    <row r="761" ht="17.25" customHeight="1"/>
+    <row r="762" ht="17.25" customHeight="1"/>
+    <row r="763" ht="17.25" customHeight="1"/>
+    <row r="764" ht="17.25" customHeight="1"/>
+    <row r="765" ht="17.25" customHeight="1"/>
+    <row r="766" ht="17.25" customHeight="1"/>
+    <row r="767" ht="17.25" customHeight="1"/>
+    <row r="768" ht="17.25" customHeight="1"/>
+    <row r="769" ht="17.25" customHeight="1"/>
+    <row r="770" ht="17.25" customHeight="1"/>
+    <row r="771" ht="17.25" customHeight="1"/>
+    <row r="772" ht="17.25" customHeight="1"/>
+    <row r="773" ht="17.25" customHeight="1"/>
+    <row r="774" ht="17.25" customHeight="1"/>
+    <row r="775" ht="17.25" customHeight="1"/>
+    <row r="776" ht="17.25" customHeight="1"/>
+    <row r="777" ht="17.25" customHeight="1"/>
+    <row r="778" ht="17.25" customHeight="1"/>
+    <row r="779" ht="17.25" customHeight="1"/>
+    <row r="780" ht="17.25" customHeight="1"/>
+    <row r="781" ht="17.25" customHeight="1"/>
+    <row r="782" ht="17.25" customHeight="1"/>
+    <row r="783" ht="17.25" customHeight="1"/>
+    <row r="784" ht="17.25" customHeight="1"/>
+    <row r="785" ht="17.25" customHeight="1"/>
+    <row r="786" ht="17.25" customHeight="1"/>
+    <row r="787" ht="17.25" customHeight="1"/>
+    <row r="788" ht="17.25" customHeight="1"/>
+    <row r="789" ht="17.25" customHeight="1"/>
+    <row r="790" ht="17.25" customHeight="1"/>
+    <row r="791" ht="17.25" customHeight="1"/>
+    <row r="792" ht="17.25" customHeight="1"/>
+    <row r="793" ht="17.25" customHeight="1"/>
+    <row r="794" ht="17.25" customHeight="1"/>
+    <row r="795" ht="17.25" customHeight="1"/>
+    <row r="796" ht="17.25" customHeight="1"/>
+    <row r="797" ht="17.25" customHeight="1"/>
+    <row r="798" ht="17.25" customHeight="1"/>
+    <row r="799" ht="17.25" customHeight="1"/>
+    <row r="800" ht="17.25" customHeight="1"/>
+    <row r="801" ht="17.25" customHeight="1"/>
+    <row r="802" ht="17.25" customHeight="1"/>
+    <row r="803" ht="17.25" customHeight="1"/>
+    <row r="804" ht="17.25" customHeight="1"/>
+    <row r="805" ht="17.25" customHeight="1"/>
+    <row r="806" ht="17.25" customHeight="1"/>
+    <row r="807" ht="17.25" customHeight="1"/>
+    <row r="808" ht="17.25" customHeight="1"/>
+    <row r="809" ht="17.25" customHeight="1"/>
+    <row r="810" ht="17.25" customHeight="1"/>
+    <row r="811" ht="17.25" customHeight="1"/>
+    <row r="812" ht="17.25" customHeight="1"/>
+    <row r="813" ht="17.25" customHeight="1"/>
+    <row r="814" ht="17.25" customHeight="1"/>
+    <row r="815" ht="17.25" customHeight="1"/>
+    <row r="816" ht="17.25" customHeight="1"/>
+    <row r="817" ht="17.25" customHeight="1"/>
+    <row r="818" ht="17.25" customHeight="1"/>
+    <row r="819" ht="17.25" customHeight="1"/>
+    <row r="820" ht="17.25" customHeight="1"/>
+    <row r="821" ht="17.25" customHeight="1"/>
+    <row r="822" ht="17.25" customHeight="1"/>
+    <row r="823" ht="17.25" customHeight="1"/>
+    <row r="824" ht="17.25" customHeight="1"/>
+    <row r="825" ht="17.25" customHeight="1"/>
+    <row r="826" ht="17.25" customHeight="1"/>
+    <row r="827" ht="17.25" customHeight="1"/>
+    <row r="828" ht="17.25" customHeight="1"/>
+    <row r="829" ht="17.25" customHeight="1"/>
+    <row r="830" ht="17.25" customHeight="1"/>
+    <row r="831" ht="17.25" customHeight="1"/>
+    <row r="832" ht="17.25" customHeight="1"/>
+    <row r="833" ht="17.25" customHeight="1"/>
+    <row r="834" ht="17.25" customHeight="1"/>
+    <row r="835" ht="17.25" customHeight="1"/>
+    <row r="836" ht="17.25" customHeight="1"/>
+    <row r="837" ht="17.25" customHeight="1"/>
+    <row r="838" ht="17.25" customHeight="1"/>
+    <row r="839" ht="17.25" customHeight="1"/>
+    <row r="840" ht="17.25" customHeight="1"/>
+    <row r="841" ht="17.25" customHeight="1"/>
+    <row r="842" ht="17.25" customHeight="1"/>
+    <row r="843" ht="17.25" customHeight="1"/>
+    <row r="844" ht="17.25" customHeight="1"/>
+    <row r="845" ht="17.25" customHeight="1"/>
+    <row r="846" ht="17.25" customHeight="1"/>
+    <row r="847" ht="17.25" customHeight="1"/>
+    <row r="848" ht="17.25" customHeight="1"/>
+    <row r="849" ht="17.25" customHeight="1"/>
+    <row r="850" ht="17.25" customHeight="1"/>
+    <row r="851" ht="17.25" customHeight="1"/>
+    <row r="852" ht="17.25" customHeight="1"/>
+    <row r="853" ht="17.25" customHeight="1"/>
+    <row r="854" ht="17.25" customHeight="1"/>
+    <row r="855" ht="17.25" customHeight="1"/>
+    <row r="856" ht="17.25" customHeight="1"/>
+    <row r="857" ht="17.25" customHeight="1"/>
+    <row r="858" ht="17.25" customHeight="1"/>
+    <row r="859" ht="17.25" customHeight="1"/>
+    <row r="860" ht="17.25" customHeight="1"/>
+    <row r="861" ht="17.25" customHeight="1"/>
+    <row r="862" ht="17.25" customHeight="1"/>
+    <row r="863" ht="17.25" customHeight="1"/>
+    <row r="864" ht="17.25" customHeight="1"/>
+    <row r="865" ht="17.25" customHeight="1"/>
+    <row r="866" ht="17.25" customHeight="1"/>
+    <row r="867" ht="17.25" customHeight="1"/>
+    <row r="868" ht="17.25" customHeight="1"/>
+    <row r="869" ht="17.25" customHeight="1"/>
+    <row r="870" ht="17.25" customHeight="1"/>
+    <row r="871" ht="17.25" customHeight="1"/>
+    <row r="872" ht="17.25" customHeight="1"/>
+    <row r="873" ht="17.25" customHeight="1"/>
+    <row r="874" ht="17.25" customHeight="1"/>
+    <row r="875" ht="17.25" customHeight="1"/>
+    <row r="876" ht="17.25" customHeight="1"/>
+    <row r="877" ht="17.25" customHeight="1"/>
+    <row r="878" ht="17.25" customHeight="1"/>
+    <row r="879" ht="17.25" customHeight="1"/>
+    <row r="880" ht="17.25" customHeight="1"/>
+    <row r="881" ht="17.25" customHeight="1"/>
+    <row r="882" ht="17.25" customHeight="1"/>
+    <row r="883" ht="17.25" customHeight="1"/>
+    <row r="884" ht="17.25" customHeight="1"/>
+    <row r="885" ht="17.25" customHeight="1"/>
+    <row r="886" ht="17.25" customHeight="1"/>
+    <row r="887" ht="17.25" customHeight="1"/>
+    <row r="888" ht="17.25" customHeight="1"/>
+    <row r="889" ht="17.25" customHeight="1"/>
+    <row r="890" ht="17.25" customHeight="1"/>
+    <row r="891" ht="17.25" customHeight="1"/>
+    <row r="892" ht="17.25" customHeight="1"/>
+    <row r="893" ht="17.25" customHeight="1"/>
+    <row r="894" ht="17.25" customHeight="1"/>
+    <row r="895" ht="17.25" customHeight="1"/>
+    <row r="896" ht="17.25" customHeight="1"/>
+    <row r="897" ht="17.25" customHeight="1"/>
+    <row r="898" ht="17.25" customHeight="1"/>
+    <row r="899" ht="17.25" customHeight="1"/>
+    <row r="900" ht="17.25" customHeight="1"/>
+    <row r="901" ht="17.25" customHeight="1"/>
+    <row r="902" ht="17.25" customHeight="1"/>
+    <row r="903" ht="17.25" customHeight="1"/>
+    <row r="904" ht="17.25" customHeight="1"/>
+    <row r="905" ht="17.25" customHeight="1"/>
+    <row r="906" ht="17.25" customHeight="1"/>
+    <row r="907" ht="17.25" customHeight="1"/>
+    <row r="908" ht="17.25" customHeight="1"/>
+    <row r="909" ht="17.25" customHeight="1"/>
+    <row r="910" ht="17.25" customHeight="1"/>
+    <row r="911" ht="17.25" customHeight="1"/>
+    <row r="912" ht="17.25" customHeight="1"/>
+    <row r="913" ht="17.25" customHeight="1"/>
+    <row r="914" ht="17.25" customHeight="1"/>
+    <row r="915" ht="17.25" customHeight="1"/>
+    <row r="916" ht="17.25" customHeight="1"/>
+    <row r="917" ht="17.25" customHeight="1"/>
+    <row r="918" ht="17.25" customHeight="1"/>
+    <row r="919" ht="17.25" customHeight="1"/>
+    <row r="920" ht="17.25" customHeight="1"/>
+    <row r="921" ht="17.25" customHeight="1"/>
+    <row r="922" ht="17.25" customHeight="1"/>
+    <row r="923" ht="17.25" customHeight="1"/>
+    <row r="924" ht="17.25" customHeight="1"/>
+    <row r="925" ht="17.25" customHeight="1"/>
+    <row r="926" ht="17.25" customHeight="1"/>
+    <row r="927" ht="17.25" customHeight="1"/>
+    <row r="928" ht="17.25" customHeight="1"/>
+    <row r="929" ht="17.25" customHeight="1"/>
+    <row r="930" ht="17.25" customHeight="1"/>
+    <row r="931" ht="17.25" customHeight="1"/>
+    <row r="932" ht="17.25" customHeight="1"/>
+    <row r="933" ht="17.25" customHeight="1"/>
+    <row r="934" ht="17.25" customHeight="1"/>
+    <row r="935" ht="17.25" customHeight="1"/>
+    <row r="936" ht="17.25" customHeight="1"/>
+    <row r="937" ht="17.25" customHeight="1"/>
+    <row r="938" ht="17.25" customHeight="1"/>
+    <row r="939" ht="17.25" customHeight="1"/>
+    <row r="940" ht="17.25" customHeight="1"/>
+    <row r="941" ht="17.25" customHeight="1"/>
+    <row r="942" ht="17.25" customHeight="1"/>
+    <row r="943" ht="17.25" customHeight="1"/>
+    <row r="944" ht="17.25" customHeight="1"/>
+    <row r="945" ht="17.25" customHeight="1"/>
+    <row r="946" ht="17.25" customHeight="1"/>
+    <row r="947" ht="17.25" customHeight="1"/>
+    <row r="948" ht="17.25" customHeight="1"/>
+    <row r="949" ht="17.25" customHeight="1"/>
+    <row r="950" ht="17.25" customHeight="1"/>
+    <row r="951" ht="17.25" customHeight="1"/>
+    <row r="952" ht="17.25" customHeight="1"/>
+    <row r="953" ht="17.25" customHeight="1"/>
+    <row r="954" ht="17.25" customHeight="1"/>
+    <row r="955" ht="17.25" customHeight="1"/>
+    <row r="956" ht="17.25" customHeight="1"/>
+    <row r="957" ht="17.25" customHeight="1"/>
+    <row r="958" ht="17.25" customHeight="1"/>
+    <row r="959" ht="17.25" customHeight="1"/>
+    <row r="960" ht="17.25" customHeight="1"/>
+    <row r="961" ht="17.25" customHeight="1"/>
+    <row r="962" ht="17.25" customHeight="1"/>
+    <row r="963" ht="17.25" customHeight="1"/>
+    <row r="964" ht="17.25" customHeight="1"/>
+    <row r="965" ht="17.25" customHeight="1"/>
+    <row r="966" ht="17.25" customHeight="1"/>
+    <row r="967" ht="17.25" customHeight="1"/>
+    <row r="968" ht="17.25" customHeight="1"/>
+    <row r="969" ht="17.25" customHeight="1"/>
+    <row r="970" ht="17.25" customHeight="1"/>
+    <row r="971" ht="17.25" customHeight="1"/>
+    <row r="972" ht="17.25" customHeight="1"/>
+    <row r="973" ht="17.25" customHeight="1"/>
+    <row r="974" ht="17.25" customHeight="1"/>
+    <row r="975" ht="17.25" customHeight="1"/>
+    <row r="976" ht="17.25" customHeight="1"/>
+    <row r="977" ht="17.25" customHeight="1"/>
+    <row r="978" ht="17.25" customHeight="1"/>
+    <row r="979" ht="17.25" customHeight="1"/>
+    <row r="980" ht="17.25" customHeight="1"/>
+    <row r="981" ht="17.25" customHeight="1"/>
+    <row r="982" ht="17.25" customHeight="1"/>
+    <row r="983" ht="17.25" customHeight="1"/>
+    <row r="984" ht="17.25" customHeight="1"/>
+    <row r="985" ht="17.25" customHeight="1"/>
+    <row r="986" ht="17.25" customHeight="1"/>
+    <row r="987" ht="17.25" customHeight="1"/>
+    <row r="988" ht="17.25" customHeight="1"/>
+    <row r="989" ht="17.25" customHeight="1"/>
+    <row r="990" ht="17.25" customHeight="1"/>
+    <row r="991" ht="17.25" customHeight="1"/>
+    <row r="992" ht="17.25" customHeight="1"/>
+    <row r="993" ht="17.25" customHeight="1"/>
+    <row r="994" ht="17.25" customHeight="1"/>
+    <row r="995" ht="17.25" customHeight="1"/>
+    <row r="996" ht="17.25" customHeight="1"/>
+    <row r="997" ht="17.25" customHeight="1"/>
+    <row r="998" ht="17.25" customHeight="1"/>
+    <row r="999" ht="17.25" customHeight="1"/>
+    <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -40,6 +40,15 @@
   </si>
   <si>
     <t>InteractableContainer_Prefab</t>
+  </si>
+  <si>
+    <t>Effect_High</t>
+  </si>
+  <si>
+    <t>Effect_Low</t>
+  </si>
+  <si>
+    <t>Effect_Normal</t>
   </si>
 </sst>
 </file>
@@ -343,9 +352,30 @@
         <v>5.0</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1"/>
-    <row r="8" ht="17.25" customHeight="1"/>
-    <row r="9" ht="17.25" customHeight="1"/>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
     <row r="10" ht="17.25" customHeight="1"/>
     <row r="11" ht="17.25" customHeight="1"/>
     <row r="12" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Effect_Normal</t>
+  </si>
+  <si>
+    <t>Door_Prefab</t>
   </si>
 </sst>
 </file>
@@ -376,7 +379,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1"/>
+    <row r="10" ht="17.25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
     <row r="11" ht="17.25" customHeight="1"/>
     <row r="12" ht="17.25" customHeight="1"/>
     <row r="13" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdong\OneDrive\바탕 화면\TeamMiniProject\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605867A4-3220-41E4-82F8-5977B943EEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C2C035-60BA-454F-813E-37B6027A37C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2016" yWindow="756" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,10 @@
   </si>
   <si>
     <t>Pool_Tool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pool_Throw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -377,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.69921875" customWidth="1"/>
@@ -420,6 +424,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -1,81 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdong\OneDrive\바탕 화면\TeamMiniProject\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C2C035-60BA-454F-813E-37B6027A37C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eGnJ0erqkwmpLAbSFXzXqD33NZjjF+BEV5V8qOaTQi0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>초기 생성될 수치</t>
+  </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>초기 생성될 수치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>InitSize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Pool_Jewel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Pool_Tool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InteractableContainer_Prefab</t>
+  </si>
+  <si>
+    <t>Effect_High</t>
+  </si>
+  <si>
+    <t>Effect_Low</t>
+  </si>
+  <si>
+    <t>Effect_Normal</t>
+  </si>
+  <si>
+    <t>Door_Prefab</t>
   </si>
   <si>
     <t>Pool_Throw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -84,55 +79,50 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="5B9BD5"/>
@@ -156,79 +146,19 @@
         <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -369,71 +299,1098 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.71"/>
+    <col customWidth="1" min="2" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B1" t="s">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" ht="17.25" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>10.0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B9" s="2">
+        <v>1.0</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
+    <row r="10" ht="17.25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5.0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
+    <row r="11" ht="17.25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>10.0</v>
       </c>
     </row>
+    <row r="12" ht="17.25" customHeight="1"/>
+    <row r="13" ht="17.25" customHeight="1"/>
+    <row r="14" ht="17.25" customHeight="1"/>
+    <row r="15" ht="17.25" customHeight="1"/>
+    <row r="16" ht="17.25" customHeight="1"/>
+    <row r="17" ht="17.25" customHeight="1"/>
+    <row r="18" ht="17.25" customHeight="1"/>
+    <row r="19" ht="17.25" customHeight="1"/>
+    <row r="20" ht="17.25" customHeight="1"/>
+    <row r="21" ht="17.25" customHeight="1"/>
+    <row r="22" ht="17.25" customHeight="1"/>
+    <row r="23" ht="17.25" customHeight="1"/>
+    <row r="24" ht="17.25" customHeight="1"/>
+    <row r="25" ht="17.25" customHeight="1"/>
+    <row r="26" ht="17.25" customHeight="1"/>
+    <row r="27" ht="17.25" customHeight="1"/>
+    <row r="28" ht="17.25" customHeight="1"/>
+    <row r="29" ht="17.25" customHeight="1"/>
+    <row r="30" ht="17.25" customHeight="1"/>
+    <row r="31" ht="17.25" customHeight="1"/>
+    <row r="32" ht="17.25" customHeight="1"/>
+    <row r="33" ht="17.25" customHeight="1"/>
+    <row r="34" ht="17.25" customHeight="1"/>
+    <row r="35" ht="17.25" customHeight="1"/>
+    <row r="36" ht="17.25" customHeight="1"/>
+    <row r="37" ht="17.25" customHeight="1"/>
+    <row r="38" ht="17.25" customHeight="1"/>
+    <row r="39" ht="17.25" customHeight="1"/>
+    <row r="40" ht="17.25" customHeight="1"/>
+    <row r="41" ht="17.25" customHeight="1"/>
+    <row r="42" ht="17.25" customHeight="1"/>
+    <row r="43" ht="17.25" customHeight="1"/>
+    <row r="44" ht="17.25" customHeight="1"/>
+    <row r="45" ht="17.25" customHeight="1"/>
+    <row r="46" ht="17.25" customHeight="1"/>
+    <row r="47" ht="17.25" customHeight="1"/>
+    <row r="48" ht="17.25" customHeight="1"/>
+    <row r="49" ht="17.25" customHeight="1"/>
+    <row r="50" ht="17.25" customHeight="1"/>
+    <row r="51" ht="17.25" customHeight="1"/>
+    <row r="52" ht="17.25" customHeight="1"/>
+    <row r="53" ht="17.25" customHeight="1"/>
+    <row r="54" ht="17.25" customHeight="1"/>
+    <row r="55" ht="17.25" customHeight="1"/>
+    <row r="56" ht="17.25" customHeight="1"/>
+    <row r="57" ht="17.25" customHeight="1"/>
+    <row r="58" ht="17.25" customHeight="1"/>
+    <row r="59" ht="17.25" customHeight="1"/>
+    <row r="60" ht="17.25" customHeight="1"/>
+    <row r="61" ht="17.25" customHeight="1"/>
+    <row r="62" ht="17.25" customHeight="1"/>
+    <row r="63" ht="17.25" customHeight="1"/>
+    <row r="64" ht="17.25" customHeight="1"/>
+    <row r="65" ht="17.25" customHeight="1"/>
+    <row r="66" ht="17.25" customHeight="1"/>
+    <row r="67" ht="17.25" customHeight="1"/>
+    <row r="68" ht="17.25" customHeight="1"/>
+    <row r="69" ht="17.25" customHeight="1"/>
+    <row r="70" ht="17.25" customHeight="1"/>
+    <row r="71" ht="17.25" customHeight="1"/>
+    <row r="72" ht="17.25" customHeight="1"/>
+    <row r="73" ht="17.25" customHeight="1"/>
+    <row r="74" ht="17.25" customHeight="1"/>
+    <row r="75" ht="17.25" customHeight="1"/>
+    <row r="76" ht="17.25" customHeight="1"/>
+    <row r="77" ht="17.25" customHeight="1"/>
+    <row r="78" ht="17.25" customHeight="1"/>
+    <row r="79" ht="17.25" customHeight="1"/>
+    <row r="80" ht="17.25" customHeight="1"/>
+    <row r="81" ht="17.25" customHeight="1"/>
+    <row r="82" ht="17.25" customHeight="1"/>
+    <row r="83" ht="17.25" customHeight="1"/>
+    <row r="84" ht="17.25" customHeight="1"/>
+    <row r="85" ht="17.25" customHeight="1"/>
+    <row r="86" ht="17.25" customHeight="1"/>
+    <row r="87" ht="17.25" customHeight="1"/>
+    <row r="88" ht="17.25" customHeight="1"/>
+    <row r="89" ht="17.25" customHeight="1"/>
+    <row r="90" ht="17.25" customHeight="1"/>
+    <row r="91" ht="17.25" customHeight="1"/>
+    <row r="92" ht="17.25" customHeight="1"/>
+    <row r="93" ht="17.25" customHeight="1"/>
+    <row r="94" ht="17.25" customHeight="1"/>
+    <row r="95" ht="17.25" customHeight="1"/>
+    <row r="96" ht="17.25" customHeight="1"/>
+    <row r="97" ht="17.25" customHeight="1"/>
+    <row r="98" ht="17.25" customHeight="1"/>
+    <row r="99" ht="17.25" customHeight="1"/>
+    <row r="100" ht="17.25" customHeight="1"/>
+    <row r="101" ht="17.25" customHeight="1"/>
+    <row r="102" ht="17.25" customHeight="1"/>
+    <row r="103" ht="17.25" customHeight="1"/>
+    <row r="104" ht="17.25" customHeight="1"/>
+    <row r="105" ht="17.25" customHeight="1"/>
+    <row r="106" ht="17.25" customHeight="1"/>
+    <row r="107" ht="17.25" customHeight="1"/>
+    <row r="108" ht="17.25" customHeight="1"/>
+    <row r="109" ht="17.25" customHeight="1"/>
+    <row r="110" ht="17.25" customHeight="1"/>
+    <row r="111" ht="17.25" customHeight="1"/>
+    <row r="112" ht="17.25" customHeight="1"/>
+    <row r="113" ht="17.25" customHeight="1"/>
+    <row r="114" ht="17.25" customHeight="1"/>
+    <row r="115" ht="17.25" customHeight="1"/>
+    <row r="116" ht="17.25" customHeight="1"/>
+    <row r="117" ht="17.25" customHeight="1"/>
+    <row r="118" ht="17.25" customHeight="1"/>
+    <row r="119" ht="17.25" customHeight="1"/>
+    <row r="120" ht="17.25" customHeight="1"/>
+    <row r="121" ht="17.25" customHeight="1"/>
+    <row r="122" ht="17.25" customHeight="1"/>
+    <row r="123" ht="17.25" customHeight="1"/>
+    <row r="124" ht="17.25" customHeight="1"/>
+    <row r="125" ht="17.25" customHeight="1"/>
+    <row r="126" ht="17.25" customHeight="1"/>
+    <row r="127" ht="17.25" customHeight="1"/>
+    <row r="128" ht="17.25" customHeight="1"/>
+    <row r="129" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1"/>
+    <row r="131" ht="17.25" customHeight="1"/>
+    <row r="132" ht="17.25" customHeight="1"/>
+    <row r="133" ht="17.25" customHeight="1"/>
+    <row r="134" ht="17.25" customHeight="1"/>
+    <row r="135" ht="17.25" customHeight="1"/>
+    <row r="136" ht="17.25" customHeight="1"/>
+    <row r="137" ht="17.25" customHeight="1"/>
+    <row r="138" ht="17.25" customHeight="1"/>
+    <row r="139" ht="17.25" customHeight="1"/>
+    <row r="140" ht="17.25" customHeight="1"/>
+    <row r="141" ht="17.25" customHeight="1"/>
+    <row r="142" ht="17.25" customHeight="1"/>
+    <row r="143" ht="17.25" customHeight="1"/>
+    <row r="144" ht="17.25" customHeight="1"/>
+    <row r="145" ht="17.25" customHeight="1"/>
+    <row r="146" ht="17.25" customHeight="1"/>
+    <row r="147" ht="17.25" customHeight="1"/>
+    <row r="148" ht="17.25" customHeight="1"/>
+    <row r="149" ht="17.25" customHeight="1"/>
+    <row r="150" ht="17.25" customHeight="1"/>
+    <row r="151" ht="17.25" customHeight="1"/>
+    <row r="152" ht="17.25" customHeight="1"/>
+    <row r="153" ht="17.25" customHeight="1"/>
+    <row r="154" ht="17.25" customHeight="1"/>
+    <row r="155" ht="17.25" customHeight="1"/>
+    <row r="156" ht="17.25" customHeight="1"/>
+    <row r="157" ht="17.25" customHeight="1"/>
+    <row r="158" ht="17.25" customHeight="1"/>
+    <row r="159" ht="17.25" customHeight="1"/>
+    <row r="160" ht="17.25" customHeight="1"/>
+    <row r="161" ht="17.25" customHeight="1"/>
+    <row r="162" ht="17.25" customHeight="1"/>
+    <row r="163" ht="17.25" customHeight="1"/>
+    <row r="164" ht="17.25" customHeight="1"/>
+    <row r="165" ht="17.25" customHeight="1"/>
+    <row r="166" ht="17.25" customHeight="1"/>
+    <row r="167" ht="17.25" customHeight="1"/>
+    <row r="168" ht="17.25" customHeight="1"/>
+    <row r="169" ht="17.25" customHeight="1"/>
+    <row r="170" ht="17.25" customHeight="1"/>
+    <row r="171" ht="17.25" customHeight="1"/>
+    <row r="172" ht="17.25" customHeight="1"/>
+    <row r="173" ht="17.25" customHeight="1"/>
+    <row r="174" ht="17.25" customHeight="1"/>
+    <row r="175" ht="17.25" customHeight="1"/>
+    <row r="176" ht="17.25" customHeight="1"/>
+    <row r="177" ht="17.25" customHeight="1"/>
+    <row r="178" ht="17.25" customHeight="1"/>
+    <row r="179" ht="17.25" customHeight="1"/>
+    <row r="180" ht="17.25" customHeight="1"/>
+    <row r="181" ht="17.25" customHeight="1"/>
+    <row r="182" ht="17.25" customHeight="1"/>
+    <row r="183" ht="17.25" customHeight="1"/>
+    <row r="184" ht="17.25" customHeight="1"/>
+    <row r="185" ht="17.25" customHeight="1"/>
+    <row r="186" ht="17.25" customHeight="1"/>
+    <row r="187" ht="17.25" customHeight="1"/>
+    <row r="188" ht="17.25" customHeight="1"/>
+    <row r="189" ht="17.25" customHeight="1"/>
+    <row r="190" ht="17.25" customHeight="1"/>
+    <row r="191" ht="17.25" customHeight="1"/>
+    <row r="192" ht="17.25" customHeight="1"/>
+    <row r="193" ht="17.25" customHeight="1"/>
+    <row r="194" ht="17.25" customHeight="1"/>
+    <row r="195" ht="17.25" customHeight="1"/>
+    <row r="196" ht="17.25" customHeight="1"/>
+    <row r="197" ht="17.25" customHeight="1"/>
+    <row r="198" ht="17.25" customHeight="1"/>
+    <row r="199" ht="17.25" customHeight="1"/>
+    <row r="200" ht="17.25" customHeight="1"/>
+    <row r="201" ht="17.25" customHeight="1"/>
+    <row r="202" ht="17.25" customHeight="1"/>
+    <row r="203" ht="17.25" customHeight="1"/>
+    <row r="204" ht="17.25" customHeight="1"/>
+    <row r="205" ht="17.25" customHeight="1"/>
+    <row r="206" ht="17.25" customHeight="1"/>
+    <row r="207" ht="17.25" customHeight="1"/>
+    <row r="208" ht="17.25" customHeight="1"/>
+    <row r="209" ht="17.25" customHeight="1"/>
+    <row r="210" ht="17.25" customHeight="1"/>
+    <row r="211" ht="17.25" customHeight="1"/>
+    <row r="212" ht="17.25" customHeight="1"/>
+    <row r="213" ht="17.25" customHeight="1"/>
+    <row r="214" ht="17.25" customHeight="1"/>
+    <row r="215" ht="17.25" customHeight="1"/>
+    <row r="216" ht="17.25" customHeight="1"/>
+    <row r="217" ht="17.25" customHeight="1"/>
+    <row r="218" ht="17.25" customHeight="1"/>
+    <row r="219" ht="17.25" customHeight="1"/>
+    <row r="220" ht="17.25" customHeight="1"/>
+    <row r="221" ht="17.25" customHeight="1"/>
+    <row r="222" ht="17.25" customHeight="1"/>
+    <row r="223" ht="17.25" customHeight="1"/>
+    <row r="224" ht="17.25" customHeight="1"/>
+    <row r="225" ht="17.25" customHeight="1"/>
+    <row r="226" ht="17.25" customHeight="1"/>
+    <row r="227" ht="17.25" customHeight="1"/>
+    <row r="228" ht="17.25" customHeight="1"/>
+    <row r="229" ht="17.25" customHeight="1"/>
+    <row r="230" ht="17.25" customHeight="1"/>
+    <row r="231" ht="17.25" customHeight="1"/>
+    <row r="232" ht="17.25" customHeight="1"/>
+    <row r="233" ht="17.25" customHeight="1"/>
+    <row r="234" ht="17.25" customHeight="1"/>
+    <row r="235" ht="17.25" customHeight="1"/>
+    <row r="236" ht="17.25" customHeight="1"/>
+    <row r="237" ht="17.25" customHeight="1"/>
+    <row r="238" ht="17.25" customHeight="1"/>
+    <row r="239" ht="17.25" customHeight="1"/>
+    <row r="240" ht="17.25" customHeight="1"/>
+    <row r="241" ht="17.25" customHeight="1"/>
+    <row r="242" ht="17.25" customHeight="1"/>
+    <row r="243" ht="17.25" customHeight="1"/>
+    <row r="244" ht="17.25" customHeight="1"/>
+    <row r="245" ht="17.25" customHeight="1"/>
+    <row r="246" ht="17.25" customHeight="1"/>
+    <row r="247" ht="17.25" customHeight="1"/>
+    <row r="248" ht="17.25" customHeight="1"/>
+    <row r="249" ht="17.25" customHeight="1"/>
+    <row r="250" ht="17.25" customHeight="1"/>
+    <row r="251" ht="17.25" customHeight="1"/>
+    <row r="252" ht="17.25" customHeight="1"/>
+    <row r="253" ht="17.25" customHeight="1"/>
+    <row r="254" ht="17.25" customHeight="1"/>
+    <row r="255" ht="17.25" customHeight="1"/>
+    <row r="256" ht="17.25" customHeight="1"/>
+    <row r="257" ht="17.25" customHeight="1"/>
+    <row r="258" ht="17.25" customHeight="1"/>
+    <row r="259" ht="17.25" customHeight="1"/>
+    <row r="260" ht="17.25" customHeight="1"/>
+    <row r="261" ht="17.25" customHeight="1"/>
+    <row r="262" ht="17.25" customHeight="1"/>
+    <row r="263" ht="17.25" customHeight="1"/>
+    <row r="264" ht="17.25" customHeight="1"/>
+    <row r="265" ht="17.25" customHeight="1"/>
+    <row r="266" ht="17.25" customHeight="1"/>
+    <row r="267" ht="17.25" customHeight="1"/>
+    <row r="268" ht="17.25" customHeight="1"/>
+    <row r="269" ht="17.25" customHeight="1"/>
+    <row r="270" ht="17.25" customHeight="1"/>
+    <row r="271" ht="17.25" customHeight="1"/>
+    <row r="272" ht="17.25" customHeight="1"/>
+    <row r="273" ht="17.25" customHeight="1"/>
+    <row r="274" ht="17.25" customHeight="1"/>
+    <row r="275" ht="17.25" customHeight="1"/>
+    <row r="276" ht="17.25" customHeight="1"/>
+    <row r="277" ht="17.25" customHeight="1"/>
+    <row r="278" ht="17.25" customHeight="1"/>
+    <row r="279" ht="17.25" customHeight="1"/>
+    <row r="280" ht="17.25" customHeight="1"/>
+    <row r="281" ht="17.25" customHeight="1"/>
+    <row r="282" ht="17.25" customHeight="1"/>
+    <row r="283" ht="17.25" customHeight="1"/>
+    <row r="284" ht="17.25" customHeight="1"/>
+    <row r="285" ht="17.25" customHeight="1"/>
+    <row r="286" ht="17.25" customHeight="1"/>
+    <row r="287" ht="17.25" customHeight="1"/>
+    <row r="288" ht="17.25" customHeight="1"/>
+    <row r="289" ht="17.25" customHeight="1"/>
+    <row r="290" ht="17.25" customHeight="1"/>
+    <row r="291" ht="17.25" customHeight="1"/>
+    <row r="292" ht="17.25" customHeight="1"/>
+    <row r="293" ht="17.25" customHeight="1"/>
+    <row r="294" ht="17.25" customHeight="1"/>
+    <row r="295" ht="17.25" customHeight="1"/>
+    <row r="296" ht="17.25" customHeight="1"/>
+    <row r="297" ht="17.25" customHeight="1"/>
+    <row r="298" ht="17.25" customHeight="1"/>
+    <row r="299" ht="17.25" customHeight="1"/>
+    <row r="300" ht="17.25" customHeight="1"/>
+    <row r="301" ht="17.25" customHeight="1"/>
+    <row r="302" ht="17.25" customHeight="1"/>
+    <row r="303" ht="17.25" customHeight="1"/>
+    <row r="304" ht="17.25" customHeight="1"/>
+    <row r="305" ht="17.25" customHeight="1"/>
+    <row r="306" ht="17.25" customHeight="1"/>
+    <row r="307" ht="17.25" customHeight="1"/>
+    <row r="308" ht="17.25" customHeight="1"/>
+    <row r="309" ht="17.25" customHeight="1"/>
+    <row r="310" ht="17.25" customHeight="1"/>
+    <row r="311" ht="17.25" customHeight="1"/>
+    <row r="312" ht="17.25" customHeight="1"/>
+    <row r="313" ht="17.25" customHeight="1"/>
+    <row r="314" ht="17.25" customHeight="1"/>
+    <row r="315" ht="17.25" customHeight="1"/>
+    <row r="316" ht="17.25" customHeight="1"/>
+    <row r="317" ht="17.25" customHeight="1"/>
+    <row r="318" ht="17.25" customHeight="1"/>
+    <row r="319" ht="17.25" customHeight="1"/>
+    <row r="320" ht="17.25" customHeight="1"/>
+    <row r="321" ht="17.25" customHeight="1"/>
+    <row r="322" ht="17.25" customHeight="1"/>
+    <row r="323" ht="17.25" customHeight="1"/>
+    <row r="324" ht="17.25" customHeight="1"/>
+    <row r="325" ht="17.25" customHeight="1"/>
+    <row r="326" ht="17.25" customHeight="1"/>
+    <row r="327" ht="17.25" customHeight="1"/>
+    <row r="328" ht="17.25" customHeight="1"/>
+    <row r="329" ht="17.25" customHeight="1"/>
+    <row r="330" ht="17.25" customHeight="1"/>
+    <row r="331" ht="17.25" customHeight="1"/>
+    <row r="332" ht="17.25" customHeight="1"/>
+    <row r="333" ht="17.25" customHeight="1"/>
+    <row r="334" ht="17.25" customHeight="1"/>
+    <row r="335" ht="17.25" customHeight="1"/>
+    <row r="336" ht="17.25" customHeight="1"/>
+    <row r="337" ht="17.25" customHeight="1"/>
+    <row r="338" ht="17.25" customHeight="1"/>
+    <row r="339" ht="17.25" customHeight="1"/>
+    <row r="340" ht="17.25" customHeight="1"/>
+    <row r="341" ht="17.25" customHeight="1"/>
+    <row r="342" ht="17.25" customHeight="1"/>
+    <row r="343" ht="17.25" customHeight="1"/>
+    <row r="344" ht="17.25" customHeight="1"/>
+    <row r="345" ht="17.25" customHeight="1"/>
+    <row r="346" ht="17.25" customHeight="1"/>
+    <row r="347" ht="17.25" customHeight="1"/>
+    <row r="348" ht="17.25" customHeight="1"/>
+    <row r="349" ht="17.25" customHeight="1"/>
+    <row r="350" ht="17.25" customHeight="1"/>
+    <row r="351" ht="17.25" customHeight="1"/>
+    <row r="352" ht="17.25" customHeight="1"/>
+    <row r="353" ht="17.25" customHeight="1"/>
+    <row r="354" ht="17.25" customHeight="1"/>
+    <row r="355" ht="17.25" customHeight="1"/>
+    <row r="356" ht="17.25" customHeight="1"/>
+    <row r="357" ht="17.25" customHeight="1"/>
+    <row r="358" ht="17.25" customHeight="1"/>
+    <row r="359" ht="17.25" customHeight="1"/>
+    <row r="360" ht="17.25" customHeight="1"/>
+    <row r="361" ht="17.25" customHeight="1"/>
+    <row r="362" ht="17.25" customHeight="1"/>
+    <row r="363" ht="17.25" customHeight="1"/>
+    <row r="364" ht="17.25" customHeight="1"/>
+    <row r="365" ht="17.25" customHeight="1"/>
+    <row r="366" ht="17.25" customHeight="1"/>
+    <row r="367" ht="17.25" customHeight="1"/>
+    <row r="368" ht="17.25" customHeight="1"/>
+    <row r="369" ht="17.25" customHeight="1"/>
+    <row r="370" ht="17.25" customHeight="1"/>
+    <row r="371" ht="17.25" customHeight="1"/>
+    <row r="372" ht="17.25" customHeight="1"/>
+    <row r="373" ht="17.25" customHeight="1"/>
+    <row r="374" ht="17.25" customHeight="1"/>
+    <row r="375" ht="17.25" customHeight="1"/>
+    <row r="376" ht="17.25" customHeight="1"/>
+    <row r="377" ht="17.25" customHeight="1"/>
+    <row r="378" ht="17.25" customHeight="1"/>
+    <row r="379" ht="17.25" customHeight="1"/>
+    <row r="380" ht="17.25" customHeight="1"/>
+    <row r="381" ht="17.25" customHeight="1"/>
+    <row r="382" ht="17.25" customHeight="1"/>
+    <row r="383" ht="17.25" customHeight="1"/>
+    <row r="384" ht="17.25" customHeight="1"/>
+    <row r="385" ht="17.25" customHeight="1"/>
+    <row r="386" ht="17.25" customHeight="1"/>
+    <row r="387" ht="17.25" customHeight="1"/>
+    <row r="388" ht="17.25" customHeight="1"/>
+    <row r="389" ht="17.25" customHeight="1"/>
+    <row r="390" ht="17.25" customHeight="1"/>
+    <row r="391" ht="17.25" customHeight="1"/>
+    <row r="392" ht="17.25" customHeight="1"/>
+    <row r="393" ht="17.25" customHeight="1"/>
+    <row r="394" ht="17.25" customHeight="1"/>
+    <row r="395" ht="17.25" customHeight="1"/>
+    <row r="396" ht="17.25" customHeight="1"/>
+    <row r="397" ht="17.25" customHeight="1"/>
+    <row r="398" ht="17.25" customHeight="1"/>
+    <row r="399" ht="17.25" customHeight="1"/>
+    <row r="400" ht="17.25" customHeight="1"/>
+    <row r="401" ht="17.25" customHeight="1"/>
+    <row r="402" ht="17.25" customHeight="1"/>
+    <row r="403" ht="17.25" customHeight="1"/>
+    <row r="404" ht="17.25" customHeight="1"/>
+    <row r="405" ht="17.25" customHeight="1"/>
+    <row r="406" ht="17.25" customHeight="1"/>
+    <row r="407" ht="17.25" customHeight="1"/>
+    <row r="408" ht="17.25" customHeight="1"/>
+    <row r="409" ht="17.25" customHeight="1"/>
+    <row r="410" ht="17.25" customHeight="1"/>
+    <row r="411" ht="17.25" customHeight="1"/>
+    <row r="412" ht="17.25" customHeight="1"/>
+    <row r="413" ht="17.25" customHeight="1"/>
+    <row r="414" ht="17.25" customHeight="1"/>
+    <row r="415" ht="17.25" customHeight="1"/>
+    <row r="416" ht="17.25" customHeight="1"/>
+    <row r="417" ht="17.25" customHeight="1"/>
+    <row r="418" ht="17.25" customHeight="1"/>
+    <row r="419" ht="17.25" customHeight="1"/>
+    <row r="420" ht="17.25" customHeight="1"/>
+    <row r="421" ht="17.25" customHeight="1"/>
+    <row r="422" ht="17.25" customHeight="1"/>
+    <row r="423" ht="17.25" customHeight="1"/>
+    <row r="424" ht="17.25" customHeight="1"/>
+    <row r="425" ht="17.25" customHeight="1"/>
+    <row r="426" ht="17.25" customHeight="1"/>
+    <row r="427" ht="17.25" customHeight="1"/>
+    <row r="428" ht="17.25" customHeight="1"/>
+    <row r="429" ht="17.25" customHeight="1"/>
+    <row r="430" ht="17.25" customHeight="1"/>
+    <row r="431" ht="17.25" customHeight="1"/>
+    <row r="432" ht="17.25" customHeight="1"/>
+    <row r="433" ht="17.25" customHeight="1"/>
+    <row r="434" ht="17.25" customHeight="1"/>
+    <row r="435" ht="17.25" customHeight="1"/>
+    <row r="436" ht="17.25" customHeight="1"/>
+    <row r="437" ht="17.25" customHeight="1"/>
+    <row r="438" ht="17.25" customHeight="1"/>
+    <row r="439" ht="17.25" customHeight="1"/>
+    <row r="440" ht="17.25" customHeight="1"/>
+    <row r="441" ht="17.25" customHeight="1"/>
+    <row r="442" ht="17.25" customHeight="1"/>
+    <row r="443" ht="17.25" customHeight="1"/>
+    <row r="444" ht="17.25" customHeight="1"/>
+    <row r="445" ht="17.25" customHeight="1"/>
+    <row r="446" ht="17.25" customHeight="1"/>
+    <row r="447" ht="17.25" customHeight="1"/>
+    <row r="448" ht="17.25" customHeight="1"/>
+    <row r="449" ht="17.25" customHeight="1"/>
+    <row r="450" ht="17.25" customHeight="1"/>
+    <row r="451" ht="17.25" customHeight="1"/>
+    <row r="452" ht="17.25" customHeight="1"/>
+    <row r="453" ht="17.25" customHeight="1"/>
+    <row r="454" ht="17.25" customHeight="1"/>
+    <row r="455" ht="17.25" customHeight="1"/>
+    <row r="456" ht="17.25" customHeight="1"/>
+    <row r="457" ht="17.25" customHeight="1"/>
+    <row r="458" ht="17.25" customHeight="1"/>
+    <row r="459" ht="17.25" customHeight="1"/>
+    <row r="460" ht="17.25" customHeight="1"/>
+    <row r="461" ht="17.25" customHeight="1"/>
+    <row r="462" ht="17.25" customHeight="1"/>
+    <row r="463" ht="17.25" customHeight="1"/>
+    <row r="464" ht="17.25" customHeight="1"/>
+    <row r="465" ht="17.25" customHeight="1"/>
+    <row r="466" ht="17.25" customHeight="1"/>
+    <row r="467" ht="17.25" customHeight="1"/>
+    <row r="468" ht="17.25" customHeight="1"/>
+    <row r="469" ht="17.25" customHeight="1"/>
+    <row r="470" ht="17.25" customHeight="1"/>
+    <row r="471" ht="17.25" customHeight="1"/>
+    <row r="472" ht="17.25" customHeight="1"/>
+    <row r="473" ht="17.25" customHeight="1"/>
+    <row r="474" ht="17.25" customHeight="1"/>
+    <row r="475" ht="17.25" customHeight="1"/>
+    <row r="476" ht="17.25" customHeight="1"/>
+    <row r="477" ht="17.25" customHeight="1"/>
+    <row r="478" ht="17.25" customHeight="1"/>
+    <row r="479" ht="17.25" customHeight="1"/>
+    <row r="480" ht="17.25" customHeight="1"/>
+    <row r="481" ht="17.25" customHeight="1"/>
+    <row r="482" ht="17.25" customHeight="1"/>
+    <row r="483" ht="17.25" customHeight="1"/>
+    <row r="484" ht="17.25" customHeight="1"/>
+    <row r="485" ht="17.25" customHeight="1"/>
+    <row r="486" ht="17.25" customHeight="1"/>
+    <row r="487" ht="17.25" customHeight="1"/>
+    <row r="488" ht="17.25" customHeight="1"/>
+    <row r="489" ht="17.25" customHeight="1"/>
+    <row r="490" ht="17.25" customHeight="1"/>
+    <row r="491" ht="17.25" customHeight="1"/>
+    <row r="492" ht="17.25" customHeight="1"/>
+    <row r="493" ht="17.25" customHeight="1"/>
+    <row r="494" ht="17.25" customHeight="1"/>
+    <row r="495" ht="17.25" customHeight="1"/>
+    <row r="496" ht="17.25" customHeight="1"/>
+    <row r="497" ht="17.25" customHeight="1"/>
+    <row r="498" ht="17.25" customHeight="1"/>
+    <row r="499" ht="17.25" customHeight="1"/>
+    <row r="500" ht="17.25" customHeight="1"/>
+    <row r="501" ht="17.25" customHeight="1"/>
+    <row r="502" ht="17.25" customHeight="1"/>
+    <row r="503" ht="17.25" customHeight="1"/>
+    <row r="504" ht="17.25" customHeight="1"/>
+    <row r="505" ht="17.25" customHeight="1"/>
+    <row r="506" ht="17.25" customHeight="1"/>
+    <row r="507" ht="17.25" customHeight="1"/>
+    <row r="508" ht="17.25" customHeight="1"/>
+    <row r="509" ht="17.25" customHeight="1"/>
+    <row r="510" ht="17.25" customHeight="1"/>
+    <row r="511" ht="17.25" customHeight="1"/>
+    <row r="512" ht="17.25" customHeight="1"/>
+    <row r="513" ht="17.25" customHeight="1"/>
+    <row r="514" ht="17.25" customHeight="1"/>
+    <row r="515" ht="17.25" customHeight="1"/>
+    <row r="516" ht="17.25" customHeight="1"/>
+    <row r="517" ht="17.25" customHeight="1"/>
+    <row r="518" ht="17.25" customHeight="1"/>
+    <row r="519" ht="17.25" customHeight="1"/>
+    <row r="520" ht="17.25" customHeight="1"/>
+    <row r="521" ht="17.25" customHeight="1"/>
+    <row r="522" ht="17.25" customHeight="1"/>
+    <row r="523" ht="17.25" customHeight="1"/>
+    <row r="524" ht="17.25" customHeight="1"/>
+    <row r="525" ht="17.25" customHeight="1"/>
+    <row r="526" ht="17.25" customHeight="1"/>
+    <row r="527" ht="17.25" customHeight="1"/>
+    <row r="528" ht="17.25" customHeight="1"/>
+    <row r="529" ht="17.25" customHeight="1"/>
+    <row r="530" ht="17.25" customHeight="1"/>
+    <row r="531" ht="17.25" customHeight="1"/>
+    <row r="532" ht="17.25" customHeight="1"/>
+    <row r="533" ht="17.25" customHeight="1"/>
+    <row r="534" ht="17.25" customHeight="1"/>
+    <row r="535" ht="17.25" customHeight="1"/>
+    <row r="536" ht="17.25" customHeight="1"/>
+    <row r="537" ht="17.25" customHeight="1"/>
+    <row r="538" ht="17.25" customHeight="1"/>
+    <row r="539" ht="17.25" customHeight="1"/>
+    <row r="540" ht="17.25" customHeight="1"/>
+    <row r="541" ht="17.25" customHeight="1"/>
+    <row r="542" ht="17.25" customHeight="1"/>
+    <row r="543" ht="17.25" customHeight="1"/>
+    <row r="544" ht="17.25" customHeight="1"/>
+    <row r="545" ht="17.25" customHeight="1"/>
+    <row r="546" ht="17.25" customHeight="1"/>
+    <row r="547" ht="17.25" customHeight="1"/>
+    <row r="548" ht="17.25" customHeight="1"/>
+    <row r="549" ht="17.25" customHeight="1"/>
+    <row r="550" ht="17.25" customHeight="1"/>
+    <row r="551" ht="17.25" customHeight="1"/>
+    <row r="552" ht="17.25" customHeight="1"/>
+    <row r="553" ht="17.25" customHeight="1"/>
+    <row r="554" ht="17.25" customHeight="1"/>
+    <row r="555" ht="17.25" customHeight="1"/>
+    <row r="556" ht="17.25" customHeight="1"/>
+    <row r="557" ht="17.25" customHeight="1"/>
+    <row r="558" ht="17.25" customHeight="1"/>
+    <row r="559" ht="17.25" customHeight="1"/>
+    <row r="560" ht="17.25" customHeight="1"/>
+    <row r="561" ht="17.25" customHeight="1"/>
+    <row r="562" ht="17.25" customHeight="1"/>
+    <row r="563" ht="17.25" customHeight="1"/>
+    <row r="564" ht="17.25" customHeight="1"/>
+    <row r="565" ht="17.25" customHeight="1"/>
+    <row r="566" ht="17.25" customHeight="1"/>
+    <row r="567" ht="17.25" customHeight="1"/>
+    <row r="568" ht="17.25" customHeight="1"/>
+    <row r="569" ht="17.25" customHeight="1"/>
+    <row r="570" ht="17.25" customHeight="1"/>
+    <row r="571" ht="17.25" customHeight="1"/>
+    <row r="572" ht="17.25" customHeight="1"/>
+    <row r="573" ht="17.25" customHeight="1"/>
+    <row r="574" ht="17.25" customHeight="1"/>
+    <row r="575" ht="17.25" customHeight="1"/>
+    <row r="576" ht="17.25" customHeight="1"/>
+    <row r="577" ht="17.25" customHeight="1"/>
+    <row r="578" ht="17.25" customHeight="1"/>
+    <row r="579" ht="17.25" customHeight="1"/>
+    <row r="580" ht="17.25" customHeight="1"/>
+    <row r="581" ht="17.25" customHeight="1"/>
+    <row r="582" ht="17.25" customHeight="1"/>
+    <row r="583" ht="17.25" customHeight="1"/>
+    <row r="584" ht="17.25" customHeight="1"/>
+    <row r="585" ht="17.25" customHeight="1"/>
+    <row r="586" ht="17.25" customHeight="1"/>
+    <row r="587" ht="17.25" customHeight="1"/>
+    <row r="588" ht="17.25" customHeight="1"/>
+    <row r="589" ht="17.25" customHeight="1"/>
+    <row r="590" ht="17.25" customHeight="1"/>
+    <row r="591" ht="17.25" customHeight="1"/>
+    <row r="592" ht="17.25" customHeight="1"/>
+    <row r="593" ht="17.25" customHeight="1"/>
+    <row r="594" ht="17.25" customHeight="1"/>
+    <row r="595" ht="17.25" customHeight="1"/>
+    <row r="596" ht="17.25" customHeight="1"/>
+    <row r="597" ht="17.25" customHeight="1"/>
+    <row r="598" ht="17.25" customHeight="1"/>
+    <row r="599" ht="17.25" customHeight="1"/>
+    <row r="600" ht="17.25" customHeight="1"/>
+    <row r="601" ht="17.25" customHeight="1"/>
+    <row r="602" ht="17.25" customHeight="1"/>
+    <row r="603" ht="17.25" customHeight="1"/>
+    <row r="604" ht="17.25" customHeight="1"/>
+    <row r="605" ht="17.25" customHeight="1"/>
+    <row r="606" ht="17.25" customHeight="1"/>
+    <row r="607" ht="17.25" customHeight="1"/>
+    <row r="608" ht="17.25" customHeight="1"/>
+    <row r="609" ht="17.25" customHeight="1"/>
+    <row r="610" ht="17.25" customHeight="1"/>
+    <row r="611" ht="17.25" customHeight="1"/>
+    <row r="612" ht="17.25" customHeight="1"/>
+    <row r="613" ht="17.25" customHeight="1"/>
+    <row r="614" ht="17.25" customHeight="1"/>
+    <row r="615" ht="17.25" customHeight="1"/>
+    <row r="616" ht="17.25" customHeight="1"/>
+    <row r="617" ht="17.25" customHeight="1"/>
+    <row r="618" ht="17.25" customHeight="1"/>
+    <row r="619" ht="17.25" customHeight="1"/>
+    <row r="620" ht="17.25" customHeight="1"/>
+    <row r="621" ht="17.25" customHeight="1"/>
+    <row r="622" ht="17.25" customHeight="1"/>
+    <row r="623" ht="17.25" customHeight="1"/>
+    <row r="624" ht="17.25" customHeight="1"/>
+    <row r="625" ht="17.25" customHeight="1"/>
+    <row r="626" ht="17.25" customHeight="1"/>
+    <row r="627" ht="17.25" customHeight="1"/>
+    <row r="628" ht="17.25" customHeight="1"/>
+    <row r="629" ht="17.25" customHeight="1"/>
+    <row r="630" ht="17.25" customHeight="1"/>
+    <row r="631" ht="17.25" customHeight="1"/>
+    <row r="632" ht="17.25" customHeight="1"/>
+    <row r="633" ht="17.25" customHeight="1"/>
+    <row r="634" ht="17.25" customHeight="1"/>
+    <row r="635" ht="17.25" customHeight="1"/>
+    <row r="636" ht="17.25" customHeight="1"/>
+    <row r="637" ht="17.25" customHeight="1"/>
+    <row r="638" ht="17.25" customHeight="1"/>
+    <row r="639" ht="17.25" customHeight="1"/>
+    <row r="640" ht="17.25" customHeight="1"/>
+    <row r="641" ht="17.25" customHeight="1"/>
+    <row r="642" ht="17.25" customHeight="1"/>
+    <row r="643" ht="17.25" customHeight="1"/>
+    <row r="644" ht="17.25" customHeight="1"/>
+    <row r="645" ht="17.25" customHeight="1"/>
+    <row r="646" ht="17.25" customHeight="1"/>
+    <row r="647" ht="17.25" customHeight="1"/>
+    <row r="648" ht="17.25" customHeight="1"/>
+    <row r="649" ht="17.25" customHeight="1"/>
+    <row r="650" ht="17.25" customHeight="1"/>
+    <row r="651" ht="17.25" customHeight="1"/>
+    <row r="652" ht="17.25" customHeight="1"/>
+    <row r="653" ht="17.25" customHeight="1"/>
+    <row r="654" ht="17.25" customHeight="1"/>
+    <row r="655" ht="17.25" customHeight="1"/>
+    <row r="656" ht="17.25" customHeight="1"/>
+    <row r="657" ht="17.25" customHeight="1"/>
+    <row r="658" ht="17.25" customHeight="1"/>
+    <row r="659" ht="17.25" customHeight="1"/>
+    <row r="660" ht="17.25" customHeight="1"/>
+    <row r="661" ht="17.25" customHeight="1"/>
+    <row r="662" ht="17.25" customHeight="1"/>
+    <row r="663" ht="17.25" customHeight="1"/>
+    <row r="664" ht="17.25" customHeight="1"/>
+    <row r="665" ht="17.25" customHeight="1"/>
+    <row r="666" ht="17.25" customHeight="1"/>
+    <row r="667" ht="17.25" customHeight="1"/>
+    <row r="668" ht="17.25" customHeight="1"/>
+    <row r="669" ht="17.25" customHeight="1"/>
+    <row r="670" ht="17.25" customHeight="1"/>
+    <row r="671" ht="17.25" customHeight="1"/>
+    <row r="672" ht="17.25" customHeight="1"/>
+    <row r="673" ht="17.25" customHeight="1"/>
+    <row r="674" ht="17.25" customHeight="1"/>
+    <row r="675" ht="17.25" customHeight="1"/>
+    <row r="676" ht="17.25" customHeight="1"/>
+    <row r="677" ht="17.25" customHeight="1"/>
+    <row r="678" ht="17.25" customHeight="1"/>
+    <row r="679" ht="17.25" customHeight="1"/>
+    <row r="680" ht="17.25" customHeight="1"/>
+    <row r="681" ht="17.25" customHeight="1"/>
+    <row r="682" ht="17.25" customHeight="1"/>
+    <row r="683" ht="17.25" customHeight="1"/>
+    <row r="684" ht="17.25" customHeight="1"/>
+    <row r="685" ht="17.25" customHeight="1"/>
+    <row r="686" ht="17.25" customHeight="1"/>
+    <row r="687" ht="17.25" customHeight="1"/>
+    <row r="688" ht="17.25" customHeight="1"/>
+    <row r="689" ht="17.25" customHeight="1"/>
+    <row r="690" ht="17.25" customHeight="1"/>
+    <row r="691" ht="17.25" customHeight="1"/>
+    <row r="692" ht="17.25" customHeight="1"/>
+    <row r="693" ht="17.25" customHeight="1"/>
+    <row r="694" ht="17.25" customHeight="1"/>
+    <row r="695" ht="17.25" customHeight="1"/>
+    <row r="696" ht="17.25" customHeight="1"/>
+    <row r="697" ht="17.25" customHeight="1"/>
+    <row r="698" ht="17.25" customHeight="1"/>
+    <row r="699" ht="17.25" customHeight="1"/>
+    <row r="700" ht="17.25" customHeight="1"/>
+    <row r="701" ht="17.25" customHeight="1"/>
+    <row r="702" ht="17.25" customHeight="1"/>
+    <row r="703" ht="17.25" customHeight="1"/>
+    <row r="704" ht="17.25" customHeight="1"/>
+    <row r="705" ht="17.25" customHeight="1"/>
+    <row r="706" ht="17.25" customHeight="1"/>
+    <row r="707" ht="17.25" customHeight="1"/>
+    <row r="708" ht="17.25" customHeight="1"/>
+    <row r="709" ht="17.25" customHeight="1"/>
+    <row r="710" ht="17.25" customHeight="1"/>
+    <row r="711" ht="17.25" customHeight="1"/>
+    <row r="712" ht="17.25" customHeight="1"/>
+    <row r="713" ht="17.25" customHeight="1"/>
+    <row r="714" ht="17.25" customHeight="1"/>
+    <row r="715" ht="17.25" customHeight="1"/>
+    <row r="716" ht="17.25" customHeight="1"/>
+    <row r="717" ht="17.25" customHeight="1"/>
+    <row r="718" ht="17.25" customHeight="1"/>
+    <row r="719" ht="17.25" customHeight="1"/>
+    <row r="720" ht="17.25" customHeight="1"/>
+    <row r="721" ht="17.25" customHeight="1"/>
+    <row r="722" ht="17.25" customHeight="1"/>
+    <row r="723" ht="17.25" customHeight="1"/>
+    <row r="724" ht="17.25" customHeight="1"/>
+    <row r="725" ht="17.25" customHeight="1"/>
+    <row r="726" ht="17.25" customHeight="1"/>
+    <row r="727" ht="17.25" customHeight="1"/>
+    <row r="728" ht="17.25" customHeight="1"/>
+    <row r="729" ht="17.25" customHeight="1"/>
+    <row r="730" ht="17.25" customHeight="1"/>
+    <row r="731" ht="17.25" customHeight="1"/>
+    <row r="732" ht="17.25" customHeight="1"/>
+    <row r="733" ht="17.25" customHeight="1"/>
+    <row r="734" ht="17.25" customHeight="1"/>
+    <row r="735" ht="17.25" customHeight="1"/>
+    <row r="736" ht="17.25" customHeight="1"/>
+    <row r="737" ht="17.25" customHeight="1"/>
+    <row r="738" ht="17.25" customHeight="1"/>
+    <row r="739" ht="17.25" customHeight="1"/>
+    <row r="740" ht="17.25" customHeight="1"/>
+    <row r="741" ht="17.25" customHeight="1"/>
+    <row r="742" ht="17.25" customHeight="1"/>
+    <row r="743" ht="17.25" customHeight="1"/>
+    <row r="744" ht="17.25" customHeight="1"/>
+    <row r="745" ht="17.25" customHeight="1"/>
+    <row r="746" ht="17.25" customHeight="1"/>
+    <row r="747" ht="17.25" customHeight="1"/>
+    <row r="748" ht="17.25" customHeight="1"/>
+    <row r="749" ht="17.25" customHeight="1"/>
+    <row r="750" ht="17.25" customHeight="1"/>
+    <row r="751" ht="17.25" customHeight="1"/>
+    <row r="752" ht="17.25" customHeight="1"/>
+    <row r="753" ht="17.25" customHeight="1"/>
+    <row r="754" ht="17.25" customHeight="1"/>
+    <row r="755" ht="17.25" customHeight="1"/>
+    <row r="756" ht="17.25" customHeight="1"/>
+    <row r="757" ht="17.25" customHeight="1"/>
+    <row r="758" ht="17.25" customHeight="1"/>
+    <row r="759" ht="17.25" customHeight="1"/>
+    <row r="760" ht="17.25" customHeight="1"/>
+    <row r="761" ht="17.25" customHeight="1"/>
+    <row r="762" ht="17.25" customHeight="1"/>
+    <row r="763" ht="17.25" customHeight="1"/>
+    <row r="764" ht="17.25" customHeight="1"/>
+    <row r="765" ht="17.25" customHeight="1"/>
+    <row r="766" ht="17.25" customHeight="1"/>
+    <row r="767" ht="17.25" customHeight="1"/>
+    <row r="768" ht="17.25" customHeight="1"/>
+    <row r="769" ht="17.25" customHeight="1"/>
+    <row r="770" ht="17.25" customHeight="1"/>
+    <row r="771" ht="17.25" customHeight="1"/>
+    <row r="772" ht="17.25" customHeight="1"/>
+    <row r="773" ht="17.25" customHeight="1"/>
+    <row r="774" ht="17.25" customHeight="1"/>
+    <row r="775" ht="17.25" customHeight="1"/>
+    <row r="776" ht="17.25" customHeight="1"/>
+    <row r="777" ht="17.25" customHeight="1"/>
+    <row r="778" ht="17.25" customHeight="1"/>
+    <row r="779" ht="17.25" customHeight="1"/>
+    <row r="780" ht="17.25" customHeight="1"/>
+    <row r="781" ht="17.25" customHeight="1"/>
+    <row r="782" ht="17.25" customHeight="1"/>
+    <row r="783" ht="17.25" customHeight="1"/>
+    <row r="784" ht="17.25" customHeight="1"/>
+    <row r="785" ht="17.25" customHeight="1"/>
+    <row r="786" ht="17.25" customHeight="1"/>
+    <row r="787" ht="17.25" customHeight="1"/>
+    <row r="788" ht="17.25" customHeight="1"/>
+    <row r="789" ht="17.25" customHeight="1"/>
+    <row r="790" ht="17.25" customHeight="1"/>
+    <row r="791" ht="17.25" customHeight="1"/>
+    <row r="792" ht="17.25" customHeight="1"/>
+    <row r="793" ht="17.25" customHeight="1"/>
+    <row r="794" ht="17.25" customHeight="1"/>
+    <row r="795" ht="17.25" customHeight="1"/>
+    <row r="796" ht="17.25" customHeight="1"/>
+    <row r="797" ht="17.25" customHeight="1"/>
+    <row r="798" ht="17.25" customHeight="1"/>
+    <row r="799" ht="17.25" customHeight="1"/>
+    <row r="800" ht="17.25" customHeight="1"/>
+    <row r="801" ht="17.25" customHeight="1"/>
+    <row r="802" ht="17.25" customHeight="1"/>
+    <row r="803" ht="17.25" customHeight="1"/>
+    <row r="804" ht="17.25" customHeight="1"/>
+    <row r="805" ht="17.25" customHeight="1"/>
+    <row r="806" ht="17.25" customHeight="1"/>
+    <row r="807" ht="17.25" customHeight="1"/>
+    <row r="808" ht="17.25" customHeight="1"/>
+    <row r="809" ht="17.25" customHeight="1"/>
+    <row r="810" ht="17.25" customHeight="1"/>
+    <row r="811" ht="17.25" customHeight="1"/>
+    <row r="812" ht="17.25" customHeight="1"/>
+    <row r="813" ht="17.25" customHeight="1"/>
+    <row r="814" ht="17.25" customHeight="1"/>
+    <row r="815" ht="17.25" customHeight="1"/>
+    <row r="816" ht="17.25" customHeight="1"/>
+    <row r="817" ht="17.25" customHeight="1"/>
+    <row r="818" ht="17.25" customHeight="1"/>
+    <row r="819" ht="17.25" customHeight="1"/>
+    <row r="820" ht="17.25" customHeight="1"/>
+    <row r="821" ht="17.25" customHeight="1"/>
+    <row r="822" ht="17.25" customHeight="1"/>
+    <row r="823" ht="17.25" customHeight="1"/>
+    <row r="824" ht="17.25" customHeight="1"/>
+    <row r="825" ht="17.25" customHeight="1"/>
+    <row r="826" ht="17.25" customHeight="1"/>
+    <row r="827" ht="17.25" customHeight="1"/>
+    <row r="828" ht="17.25" customHeight="1"/>
+    <row r="829" ht="17.25" customHeight="1"/>
+    <row r="830" ht="17.25" customHeight="1"/>
+    <row r="831" ht="17.25" customHeight="1"/>
+    <row r="832" ht="17.25" customHeight="1"/>
+    <row r="833" ht="17.25" customHeight="1"/>
+    <row r="834" ht="17.25" customHeight="1"/>
+    <row r="835" ht="17.25" customHeight="1"/>
+    <row r="836" ht="17.25" customHeight="1"/>
+    <row r="837" ht="17.25" customHeight="1"/>
+    <row r="838" ht="17.25" customHeight="1"/>
+    <row r="839" ht="17.25" customHeight="1"/>
+    <row r="840" ht="17.25" customHeight="1"/>
+    <row r="841" ht="17.25" customHeight="1"/>
+    <row r="842" ht="17.25" customHeight="1"/>
+    <row r="843" ht="17.25" customHeight="1"/>
+    <row r="844" ht="17.25" customHeight="1"/>
+    <row r="845" ht="17.25" customHeight="1"/>
+    <row r="846" ht="17.25" customHeight="1"/>
+    <row r="847" ht="17.25" customHeight="1"/>
+    <row r="848" ht="17.25" customHeight="1"/>
+    <row r="849" ht="17.25" customHeight="1"/>
+    <row r="850" ht="17.25" customHeight="1"/>
+    <row r="851" ht="17.25" customHeight="1"/>
+    <row r="852" ht="17.25" customHeight="1"/>
+    <row r="853" ht="17.25" customHeight="1"/>
+    <row r="854" ht="17.25" customHeight="1"/>
+    <row r="855" ht="17.25" customHeight="1"/>
+    <row r="856" ht="17.25" customHeight="1"/>
+    <row r="857" ht="17.25" customHeight="1"/>
+    <row r="858" ht="17.25" customHeight="1"/>
+    <row r="859" ht="17.25" customHeight="1"/>
+    <row r="860" ht="17.25" customHeight="1"/>
+    <row r="861" ht="17.25" customHeight="1"/>
+    <row r="862" ht="17.25" customHeight="1"/>
+    <row r="863" ht="17.25" customHeight="1"/>
+    <row r="864" ht="17.25" customHeight="1"/>
+    <row r="865" ht="17.25" customHeight="1"/>
+    <row r="866" ht="17.25" customHeight="1"/>
+    <row r="867" ht="17.25" customHeight="1"/>
+    <row r="868" ht="17.25" customHeight="1"/>
+    <row r="869" ht="17.25" customHeight="1"/>
+    <row r="870" ht="17.25" customHeight="1"/>
+    <row r="871" ht="17.25" customHeight="1"/>
+    <row r="872" ht="17.25" customHeight="1"/>
+    <row r="873" ht="17.25" customHeight="1"/>
+    <row r="874" ht="17.25" customHeight="1"/>
+    <row r="875" ht="17.25" customHeight="1"/>
+    <row r="876" ht="17.25" customHeight="1"/>
+    <row r="877" ht="17.25" customHeight="1"/>
+    <row r="878" ht="17.25" customHeight="1"/>
+    <row r="879" ht="17.25" customHeight="1"/>
+    <row r="880" ht="17.25" customHeight="1"/>
+    <row r="881" ht="17.25" customHeight="1"/>
+    <row r="882" ht="17.25" customHeight="1"/>
+    <row r="883" ht="17.25" customHeight="1"/>
+    <row r="884" ht="17.25" customHeight="1"/>
+    <row r="885" ht="17.25" customHeight="1"/>
+    <row r="886" ht="17.25" customHeight="1"/>
+    <row r="887" ht="17.25" customHeight="1"/>
+    <row r="888" ht="17.25" customHeight="1"/>
+    <row r="889" ht="17.25" customHeight="1"/>
+    <row r="890" ht="17.25" customHeight="1"/>
+    <row r="891" ht="17.25" customHeight="1"/>
+    <row r="892" ht="17.25" customHeight="1"/>
+    <row r="893" ht="17.25" customHeight="1"/>
+    <row r="894" ht="17.25" customHeight="1"/>
+    <row r="895" ht="17.25" customHeight="1"/>
+    <row r="896" ht="17.25" customHeight="1"/>
+    <row r="897" ht="17.25" customHeight="1"/>
+    <row r="898" ht="17.25" customHeight="1"/>
+    <row r="899" ht="17.25" customHeight="1"/>
+    <row r="900" ht="17.25" customHeight="1"/>
+    <row r="901" ht="17.25" customHeight="1"/>
+    <row r="902" ht="17.25" customHeight="1"/>
+    <row r="903" ht="17.25" customHeight="1"/>
+    <row r="904" ht="17.25" customHeight="1"/>
+    <row r="905" ht="17.25" customHeight="1"/>
+    <row r="906" ht="17.25" customHeight="1"/>
+    <row r="907" ht="17.25" customHeight="1"/>
+    <row r="908" ht="17.25" customHeight="1"/>
+    <row r="909" ht="17.25" customHeight="1"/>
+    <row r="910" ht="17.25" customHeight="1"/>
+    <row r="911" ht="17.25" customHeight="1"/>
+    <row r="912" ht="17.25" customHeight="1"/>
+    <row r="913" ht="17.25" customHeight="1"/>
+    <row r="914" ht="17.25" customHeight="1"/>
+    <row r="915" ht="17.25" customHeight="1"/>
+    <row r="916" ht="17.25" customHeight="1"/>
+    <row r="917" ht="17.25" customHeight="1"/>
+    <row r="918" ht="17.25" customHeight="1"/>
+    <row r="919" ht="17.25" customHeight="1"/>
+    <row r="920" ht="17.25" customHeight="1"/>
+    <row r="921" ht="17.25" customHeight="1"/>
+    <row r="922" ht="17.25" customHeight="1"/>
+    <row r="923" ht="17.25" customHeight="1"/>
+    <row r="924" ht="17.25" customHeight="1"/>
+    <row r="925" ht="17.25" customHeight="1"/>
+    <row r="926" ht="17.25" customHeight="1"/>
+    <row r="927" ht="17.25" customHeight="1"/>
+    <row r="928" ht="17.25" customHeight="1"/>
+    <row r="929" ht="17.25" customHeight="1"/>
+    <row r="930" ht="17.25" customHeight="1"/>
+    <row r="931" ht="17.25" customHeight="1"/>
+    <row r="932" ht="17.25" customHeight="1"/>
+    <row r="933" ht="17.25" customHeight="1"/>
+    <row r="934" ht="17.25" customHeight="1"/>
+    <row r="935" ht="17.25" customHeight="1"/>
+    <row r="936" ht="17.25" customHeight="1"/>
+    <row r="937" ht="17.25" customHeight="1"/>
+    <row r="938" ht="17.25" customHeight="1"/>
+    <row r="939" ht="17.25" customHeight="1"/>
+    <row r="940" ht="17.25" customHeight="1"/>
+    <row r="941" ht="17.25" customHeight="1"/>
+    <row r="942" ht="17.25" customHeight="1"/>
+    <row r="943" ht="17.25" customHeight="1"/>
+    <row r="944" ht="17.25" customHeight="1"/>
+    <row r="945" ht="17.25" customHeight="1"/>
+    <row r="946" ht="17.25" customHeight="1"/>
+    <row r="947" ht="17.25" customHeight="1"/>
+    <row r="948" ht="17.25" customHeight="1"/>
+    <row r="949" ht="17.25" customHeight="1"/>
+    <row r="950" ht="17.25" customHeight="1"/>
+    <row r="951" ht="17.25" customHeight="1"/>
+    <row r="952" ht="17.25" customHeight="1"/>
+    <row r="953" ht="17.25" customHeight="1"/>
+    <row r="954" ht="17.25" customHeight="1"/>
+    <row r="955" ht="17.25" customHeight="1"/>
+    <row r="956" ht="17.25" customHeight="1"/>
+    <row r="957" ht="17.25" customHeight="1"/>
+    <row r="958" ht="17.25" customHeight="1"/>
+    <row r="959" ht="17.25" customHeight="1"/>
+    <row r="960" ht="17.25" customHeight="1"/>
+    <row r="961" ht="17.25" customHeight="1"/>
+    <row r="962" ht="17.25" customHeight="1"/>
+    <row r="963" ht="17.25" customHeight="1"/>
+    <row r="964" ht="17.25" customHeight="1"/>
+    <row r="965" ht="17.25" customHeight="1"/>
+    <row r="966" ht="17.25" customHeight="1"/>
+    <row r="967" ht="17.25" customHeight="1"/>
+    <row r="968" ht="17.25" customHeight="1"/>
+    <row r="969" ht="17.25" customHeight="1"/>
+    <row r="970" ht="17.25" customHeight="1"/>
+    <row r="971" ht="17.25" customHeight="1"/>
+    <row r="972" ht="17.25" customHeight="1"/>
+    <row r="973" ht="17.25" customHeight="1"/>
+    <row r="974" ht="17.25" customHeight="1"/>
+    <row r="975" ht="17.25" customHeight="1"/>
+    <row r="976" ht="17.25" customHeight="1"/>
+    <row r="977" ht="17.25" customHeight="1"/>
+    <row r="978" ht="17.25" customHeight="1"/>
+    <row r="979" ht="17.25" customHeight="1"/>
+    <row r="980" ht="17.25" customHeight="1"/>
+    <row r="981" ht="17.25" customHeight="1"/>
+    <row r="982" ht="17.25" customHeight="1"/>
+    <row r="983" ht="17.25" customHeight="1"/>
+    <row r="984" ht="17.25" customHeight="1"/>
+    <row r="985" ht="17.25" customHeight="1"/>
+    <row r="986" ht="17.25" customHeight="1"/>
+    <row r="987" ht="17.25" customHeight="1"/>
+    <row r="988" ht="17.25" customHeight="1"/>
+    <row r="989" ht="17.25" customHeight="1"/>
+    <row r="990" ht="17.25" customHeight="1"/>
+    <row r="991" ht="17.25" customHeight="1"/>
+    <row r="992" ht="17.25" customHeight="1"/>
+    <row r="993" ht="17.25" customHeight="1"/>
+    <row r="994" ht="17.25" customHeight="1"/>
+    <row r="995" ht="17.25" customHeight="1"/>
+    <row r="996" ht="17.25" customHeight="1"/>
+    <row r="997" ht="17.25" customHeight="1"/>
+    <row r="998" ht="17.25" customHeight="1"/>
+    <row r="999" ht="17.25" customHeight="1"/>
+    <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eGnJ0erqkwmpLAbSFXzXqD33NZjjF+BEV5V8qOaTQi0="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -39,6 +50,9 @@
     <t>Pool_Tool</t>
   </si>
   <si>
+    <t>Pool_Painting</t>
+  </si>
+  <si>
     <t>InteractableContainer_Prefab</t>
   </si>
   <si>
@@ -57,56 +71,894 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -296,26 +1148,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1001"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.71"/>
-    <col customWidth="1" min="2" max="26" width="8.71"/>
+    <col min="1" max="1" width="13.7777777777778" customWidth="1"/>
+    <col min="2" max="26" width="8.71296296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -323,7 +1175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -331,63 +1183,70 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+    <row r="6" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2">
-        <v>5.0</v>
+      <c r="B6" s="1">
+        <v>5</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2">
-        <v>1.0</v>
+      <c r="B7">
+        <v>5</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+    <row r="8" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2">
-        <v>1.0</v>
+      <c r="B8">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2">
-        <v>1.0</v>
+      <c r="B9">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="10" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2">
-        <v>5.0</v>
+      <c r="B10">
+        <v>1</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1"/>
+    <row r="11" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
     <row r="12" ht="17.25" customHeight="1"/>
     <row r="13" ht="17.25" customHeight="1"/>
     <row r="14" ht="17.25" customHeight="1"/>
@@ -1377,10 +2236,10 @@
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
+    <row r="1001" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Pool_Painting</t>
+  </si>
+  <si>
+    <t>Pool_Statue</t>
   </si>
   <si>
     <t>InteractableContainer_Prefab</t>
@@ -1155,7 +1158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1001"/>
+  <dimension ref="A1:B1002"/>
   <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13.7777777777778" customWidth="1"/>
@@ -1208,10 +1211,10 @@
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>5</v>
       </c>
     </row>
@@ -1220,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:2">
@@ -1244,10 +1247,17 @@
         <v>12</v>
       </c>
       <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
         <v>5</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1"/>
     <row r="13" ht="17.25" customHeight="1"/>
     <row r="14" ht="17.25" customHeight="1"/>
     <row r="15" ht="17.25" customHeight="1"/>
@@ -2237,6 +2247,7 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
     <row r="1001" ht="17.25" customHeight="1"/>
+    <row r="1002" ht="17.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="landscape"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eGnJ0erqkwmpLAbSFXzXqD33NZjjF+BEV5V8qOaTQi0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="UaRGCDEO2fZmoL8i2UT90VJqggYIZuiSsLdN/M4caX8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -39,6 +39,9 @@
     <t>Pool_Tool</t>
   </si>
   <si>
+    <t>Pool_Painting</t>
+  </si>
+  <si>
     <t>InteractableContainer_Prefab</t>
   </si>
   <si>
@@ -55,6 +58,21 @@
   </si>
   <si>
     <t>Pool_Throw</t>
+  </si>
+  <si>
+    <t>Pool_Bullet</t>
+  </si>
+  <si>
+    <t>Police_Normal</t>
+  </si>
+  <si>
+    <t>Police_Shoot</t>
+  </si>
+  <si>
+    <t>Police_Throw</t>
+  </si>
+  <si>
+    <t>Police_Dog</t>
   </si>
 </sst>
 </file>
@@ -363,7 +381,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -387,7 +405,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -395,15 +413,57 @@
         <v>12</v>
       </c>
       <c r="B11" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
         <v>10.0</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1"/>
-    <row r="13" ht="17.25" customHeight="1"/>
-    <row r="14" ht="17.25" customHeight="1"/>
-    <row r="15" ht="17.25" customHeight="1"/>
-    <row r="16" ht="17.25" customHeight="1"/>
-    <row r="17" ht="17.25" customHeight="1"/>
+    <row r="13" ht="17.25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16" ht="17.25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="17" ht="17.25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
     <row r="18" ht="17.25" customHeight="1"/>
     <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>
@@ -1387,6 +1447,7 @@
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
+    <row r="1001" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="UaRGCDEO2fZmoL8i2UT90VJqggYIZuiSsLdN/M4caX8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="keCrCjskTA0Ej1HLqAWgoZI3YDVhahkDWEwAZz8nQqk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Pool_Painting</t>
+  </si>
+  <si>
+    <t>Pool_Statue</t>
   </si>
   <si>
     <t>InteractableContainer_Prefab</t>
@@ -389,7 +392,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -413,7 +416,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -421,7 +424,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -437,7 +440,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -464,7 +467,14 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1"/>
+    <row r="18" ht="17.25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
     <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>
     <row r="21" ht="17.25" customHeight="1"/>
@@ -1448,6 +1458,7 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
     <row r="1001" ht="17.25" customHeight="1"/>
+    <row r="1002" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="keCrCjskTA0Ej1HLqAWgoZI3YDVhahkDWEwAZz8nQqk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -69,899 +58,79 @@
   </si>
   <si>
     <t>Door_Prefab</t>
+  </si>
+  <si>
+    <t>Pool_Throw</t>
+  </si>
+  <si>
+    <t>Pool_Bullet</t>
+  </si>
+  <si>
+    <t>Police_Normal</t>
+  </si>
+  <si>
+    <t>Police_Shoot</t>
+  </si>
+  <si>
+    <t>Police_Throw</t>
+  </si>
+  <si>
+    <t>Police_Dog</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="1">
+    <border/>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1151,26 +320,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B1002"/>
-  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.7777777777778" customWidth="1"/>
-    <col min="2" max="26" width="8.71296296296296" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.71"/>
+    <col customWidth="1" min="2" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:2">
+    <row r="1" ht="17.25" customHeight="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:2">
+    <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1178,7 +347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:2">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1186,84 +355,126 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1" spans="1:2">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A6" s="1" t="s">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="B6" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A8" t="s">
+      <c r="B7" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A9" t="s">
+      <c r="B8" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A10" t="s">
+      <c r="B9" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A11" t="s">
+      <c r="B10" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11" ht="17.25" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A12" t="s">
+      <c r="B11" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1"/>
-    <row r="14" ht="17.25" customHeight="1"/>
-    <row r="15" ht="17.25" customHeight="1"/>
-    <row r="16" ht="17.25" customHeight="1"/>
-    <row r="17" ht="17.25" customHeight="1"/>
-    <row r="18" ht="17.25" customHeight="1"/>
+      <c r="B12" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16" ht="17.25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="17" ht="17.25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="18" ht="17.25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
     <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>
     <row r="21" ht="17.25" customHeight="1"/>
@@ -2249,8 +1460,9 @@
     <row r="1001" ht="17.25" customHeight="1"/>
     <row r="1002" ht="17.25" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -33,10 +33,10 @@
     <t>InitSize</t>
   </si>
   <si>
-    <t>Pool_Jewel</t>
-  </si>
-  <si>
-    <t>Pool_Tool</t>
+    <t>JewelObject</t>
+  </si>
+  <si>
+    <t>ToolObject</t>
   </si>
   <si>
     <t>Pool_Painting</t>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Police_Dog</t>
+  </si>
+  <si>
+    <t>JunkObject</t>
   </si>
 </sst>
 </file>
@@ -330,7 +333,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.71"/>
+    <col customWidth="1" min="1" max="1" width="14.43"/>
     <col customWidth="1" min="2" max="26" width="8.71"/>
   </cols>
   <sheetData>
@@ -356,7 +359,7 @@
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
@@ -364,7 +367,7 @@
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
@@ -475,7 +478,14 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1"/>
+    <row r="19" ht="17.25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
     <row r="20" ht="17.25" customHeight="1"/>
     <row r="21" ht="17.25" customHeight="1"/>
     <row r="22" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="keCrCjskTA0Ej1HLqAWgoZI3YDVhahkDWEwAZz8nQqk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="UaRGCDEO2fZmoL8i2UT90VJqggYIZuiSsLdN/M4caX8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -33,13 +33,10 @@
     <t>InitSize</t>
   </si>
   <si>
-    <t>Pool_Jewel</t>
+    <t>ItemObject</t>
   </si>
   <si>
     <t>Pool_Tool</t>
-  </si>
-  <si>
-    <t>Pool_Painting</t>
   </si>
   <si>
     <t>Pool_Statue</t>
@@ -330,7 +327,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.71"/>
+    <col customWidth="1" min="1" max="1" width="14.43"/>
     <col customWidth="1" min="2" max="26" width="8.71"/>
   </cols>
   <sheetData>
@@ -356,15 +353,15 @@
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
-        <v>10.0</v>
+      <c r="B4" s="2">
+        <v>20.0</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
@@ -392,7 +389,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -416,7 +413,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -424,7 +421,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -440,7 +437,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -467,14 +464,7 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
+    <row r="18" ht="17.25" customHeight="1"/>
     <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>
     <row r="21" ht="17.25" customHeight="1"/>
@@ -1458,7 +1448,6 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
     <row r="1001" ht="17.25" customHeight="1"/>
-    <row r="1002" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="keCrCjskTA0Ej1HLqAWgoZI3YDVhahkDWEwAZz8nQqk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="UaRGCDEO2fZmoL8i2UT90VJqggYIZuiSsLdN/M4caX8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -33,13 +33,10 @@
     <t>InitSize</t>
   </si>
   <si>
-    <t>JewelObject</t>
-  </si>
-  <si>
-    <t>ToolObject</t>
-  </si>
-  <si>
-    <t>Pool_Painting</t>
+    <t>ItemObject</t>
+  </si>
+  <si>
+    <t>Pool_Tool</t>
   </si>
   <si>
     <t>Pool_Statue</t>
@@ -76,9 +73,6 @@
   </si>
   <si>
     <t>Police_Dog</t>
-  </si>
-  <si>
-    <t>JunkObject</t>
   </si>
 </sst>
 </file>
@@ -362,8 +356,8 @@
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
-        <v>10.0</v>
+      <c r="B4" s="2">
+        <v>20.0</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -395,7 +389,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -419,7 +413,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -427,7 +421,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -443,7 +437,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -470,22 +464,8 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="19" ht="17.25" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="2">
-        <v>10.0</v>
-      </c>
-    </row>
+    <row r="18" ht="17.25" customHeight="1"/>
+    <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>
     <row r="21" ht="17.25" customHeight="1"/>
     <row r="22" ht="17.25" customHeight="1"/>
@@ -1468,7 +1448,6 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
     <row r="1001" ht="17.25" customHeight="1"/>
-    <row r="1002" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Police_Throw</t>
-  </si>
-  <si>
-    <t>Police_Dog</t>
   </si>
 </sst>
 </file>
@@ -456,14 +453,7 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
+    <row r="17" ht="17.25" customHeight="1"/>
     <row r="18" ht="17.25" customHeight="1"/>
     <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="UaRGCDEO2fZmoL8i2UT90VJqggYIZuiSsLdN/M4caX8="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -71,63 +82,898 @@
   <si>
     <t>Police_Throw</t>
   </si>
-  <si>
-    <t>Police_Dog</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -317,26 +1163,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B1001"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.43"/>
-    <col customWidth="1" min="2" max="26" width="8.71"/>
+    <col min="1" max="1" width="14.4259259259259" customWidth="1"/>
+    <col min="2" max="26" width="8.71296296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -344,7 +1190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -352,118 +1198,111 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
-        <v>20.0</v>
+      <c r="B4">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+    <row r="6" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2">
-        <v>5.0</v>
+      <c r="B6">
+        <v>5</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2">
-        <v>5.0</v>
+      <c r="B7">
+        <v>5</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+    <row r="8" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2">
-        <v>1.0</v>
+      <c r="B8">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2">
-        <v>1.0</v>
+      <c r="B9">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="10" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2">
-        <v>1.0</v>
+      <c r="B10">
+        <v>1</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="11" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2">
-        <v>5.0</v>
+      <c r="B11">
+        <v>5</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="A12" s="2" t="s">
+    <row r="12" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="2">
-        <v>10.0</v>
+      <c r="B12">
+        <v>10</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="A13" s="2" t="s">
+    <row r="13" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="2">
-        <v>10.0</v>
+      <c r="B13">
+        <v>10</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="A14" s="2" t="s">
+    <row r="14" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="2">
-        <v>3.0</v>
+      <c r="B14">
+        <v>3</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="A15" s="2" t="s">
+    <row r="15" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="2">
-        <v>3.0</v>
+      <c r="B15">
+        <v>3</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
-      <c r="A16" s="2" t="s">
+    <row r="16" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2">
-        <v>3.0</v>
+      <c r="B16">
+        <v>3</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
+    <row r="17" ht="17.25" customHeight="1"/>
     <row r="18" ht="17.25" customHeight="1"/>
     <row r="19" ht="17.25" customHeight="1"/>
     <row r="20" ht="17.25" customHeight="1"/>
@@ -1449,9 +2288,8 @@
     <row r="1000" ht="17.25" customHeight="1"/>
     <row r="1001" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>BaseTrap</t>
+  </si>
+  <si>
+    <t>MushroomTrap</t>
+  </si>
+  <si>
+    <t>Escape</t>
   </si>
 </sst>
 </file>
@@ -516,8 +522,22 @@
         <v>15.0</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1"/>
-    <row r="23" ht="17.25" customHeight="1"/>
+    <row r="22" ht="17.25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="2">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2">
+        <v>7.0</v>
+      </c>
+    </row>
     <row r="24" ht="17.25" customHeight="1"/>
     <row r="25" ht="17.25" customHeight="1"/>
     <row r="26" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Pool.xlsx
+++ b/JsonConverter/ExcelFiles/Pool.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>초기 생성될 수치</t>
   </si>
@@ -91,6 +91,66 @@
   </si>
   <si>
     <t>Escape</t>
+  </si>
+  <si>
+    <t>MapGrid</t>
+  </si>
+  <si>
+    <t>All Direction Corridor</t>
+  </si>
+  <si>
+    <t>Vertical Corridor</t>
+  </si>
+  <si>
+    <t>Horizontal Corridor</t>
+  </si>
+  <si>
+    <t>RightTop Corridor</t>
+  </si>
+  <si>
+    <t>RightDown Corridor</t>
+  </si>
+  <si>
+    <t>LeftTop Corridor</t>
+  </si>
+  <si>
+    <t>LeftDown Corridor</t>
+  </si>
+  <si>
+    <t>T Corridor1</t>
+  </si>
+  <si>
+    <t>T Corridor2</t>
+  </si>
+  <si>
+    <t>T Corridor3</t>
+  </si>
+  <si>
+    <t>T Corridor4</t>
+  </si>
+  <si>
+    <t>Room1</t>
+  </si>
+  <si>
+    <t>Demo Room1</t>
+  </si>
+  <si>
+    <t>Demo Room2</t>
+  </si>
+  <si>
+    <t>Demo Room3</t>
+  </si>
+  <si>
+    <t>Demo Room4</t>
+  </si>
+  <si>
+    <t>Demo Room5</t>
+  </si>
+  <si>
+    <t>Demo Room6</t>
+  </si>
+  <si>
+    <t>Demo Room7</t>
   </si>
 </sst>
 </file>
@@ -538,26 +598,166 @@
         <v>7.0</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1"/>
-    <row r="25" ht="17.25" customHeight="1"/>
-    <row r="26" ht="17.25" customHeight="1"/>
-    <row r="27" ht="17.25" customHeight="1"/>
-    <row r="28" ht="17.25" customHeight="1"/>
-    <row r="29" ht="17.25" customHeight="1"/>
-    <row r="30" ht="17.25" customHeight="1"/>
-    <row r="31" ht="17.25" customHeight="1"/>
-    <row r="32" ht="17.25" customHeight="1"/>
-    <row r="33" ht="17.25" customHeight="1"/>
-    <row r="34" ht="17.25" customHeight="1"/>
-    <row r="35" ht="17.25" customHeight="1"/>
-    <row r="36" ht="17.25" customHeight="1"/>
-    <row r="37" ht="17.25" customHeight="1"/>
-    <row r="38" ht="17.25" customHeight="1"/>
-    <row r="39" ht="17.25" customHeight="1"/>
-    <row r="40" ht="17.25" customHeight="1"/>
-    <row r="41" ht="17.25" customHeight="1"/>
-    <row r="42" ht="17.25" customHeight="1"/>
-    <row r="43" ht="17.25" customHeight="1"/>
+    <row r="24" ht="17.25" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="25" ht="17.25" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="36" ht="17.25" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="39" ht="17.25" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
     <row r="44" ht="17.25" customHeight="1"/>
     <row r="45" ht="17.25" customHeight="1"/>
     <row r="46" ht="17.25" customHeight="1"/>
